--- a/Att.xlsx
+++ b/Att.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\寶可夢\Pokemon_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5043B545-F74C-4176-B51B-1378F27E4B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BB8643-DDF1-4863-A158-CDE2F372B7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3162,93 +3162,138 @@
         </row>
         <row r="169">
           <cell r="AM169" t="str">
-            <v/>
+            <v>鴨嘴炎獸</v>
           </cell>
           <cell r="AN169" t="str">
-            <v/>
-          </cell>
-          <cell r="AP169" t="str">
-            <v/>
+            <v>火</v>
+          </cell>
+          <cell r="AO169" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP169">
+            <v>207</v>
+          </cell>
+          <cell r="AQ169" t="str">
+            <v>D</v>
           </cell>
         </row>
         <row r="170">
           <cell r="AM170" t="str">
-            <v/>
+            <v>鴨嘴炎獸</v>
           </cell>
           <cell r="AN170" t="str">
-            <v/>
-          </cell>
-          <cell r="AP170" t="str">
-            <v/>
+            <v>格鬥</v>
+          </cell>
+          <cell r="AO170" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="AP170">
+            <v>207</v>
+          </cell>
+          <cell r="AQ170" t="str">
+            <v>D</v>
           </cell>
         </row>
         <row r="171">
           <cell r="AM171" t="str">
-            <v/>
+            <v>超甲狂犀</v>
           </cell>
           <cell r="AN171" t="str">
-            <v/>
-          </cell>
-          <cell r="AP171" t="str">
-            <v/>
+            <v>地面</v>
+          </cell>
+          <cell r="AO171" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP171">
+            <v>202</v>
+          </cell>
+          <cell r="AQ171" t="str">
+            <v>D</v>
           </cell>
         </row>
         <row r="172">
           <cell r="AM172" t="str">
-            <v/>
+            <v>超甲狂犀</v>
           </cell>
           <cell r="AN172" t="str">
-            <v/>
-          </cell>
-          <cell r="AP172" t="str">
-            <v/>
+            <v>岩石</v>
+          </cell>
+          <cell r="AO172" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP172">
+            <v>202</v>
+          </cell>
+          <cell r="AQ172" t="str">
+            <v>D</v>
           </cell>
         </row>
         <row r="173">
           <cell r="AM173" t="str">
-            <v/>
+            <v>帝牙盧卡</v>
           </cell>
           <cell r="AN173" t="str">
-            <v/>
-          </cell>
-          <cell r="AP173" t="str">
-            <v/>
+            <v>鋼</v>
+          </cell>
+          <cell r="AO173" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP173">
+            <v>225</v>
+          </cell>
+          <cell r="AQ173" t="str">
+            <v>D</v>
           </cell>
         </row>
         <row r="174">
           <cell r="AM174" t="str">
-            <v/>
+            <v>帝牙盧卡</v>
           </cell>
           <cell r="AN174" t="str">
-            <v/>
-          </cell>
-          <cell r="AP174" t="str">
-            <v/>
+            <v>龍</v>
+          </cell>
+          <cell r="AO174" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP174">
+            <v>225</v>
+          </cell>
+          <cell r="AQ174" t="str">
+            <v>D</v>
           </cell>
         </row>
         <row r="175">
           <cell r="AM175" t="str">
-            <v/>
+            <v>帕路奇亞</v>
           </cell>
           <cell r="AN175" t="str">
-            <v/>
-          </cell>
-          <cell r="AP175" t="str">
-            <v/>
+            <v>龍</v>
+          </cell>
+          <cell r="AO175" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP175">
+            <v>233</v>
+          </cell>
+          <cell r="AQ175" t="str">
+            <v>D</v>
           </cell>
         </row>
         <row r="176">
           <cell r="AM176" t="str">
-            <v/>
+            <v>超極巨鋁鋼龍</v>
           </cell>
           <cell r="AN176" t="str">
-            <v/>
-          </cell>
-          <cell r="AP176" t="str">
-            <v/>
+            <v>鋼</v>
+          </cell>
+          <cell r="AO176" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP176">
+            <v>201</v>
           </cell>
           <cell r="AQ176" t="str">
-            <v/>
+            <v>G</v>
           </cell>
         </row>
         <row r="177">
@@ -8760,177 +8805,177 @@
     <row r="168" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B168" s="13" t="str">
         <f>IF([1]攻守數據!AM169 = "", "", [1]攻守數據!AM169)</f>
-        <v/>
+        <v>鴨嘴炎獸</v>
       </c>
       <c r="C168" s="13" t="str">
         <f>IF([1]攻守數據!AN169 = "", "", [1]攻守數據!AN169)</f>
-        <v/>
+        <v>火</v>
       </c>
       <c r="D168" s="13" t="str">
         <f>IF([1]攻守數據!AO169 = "", "", [1]攻守數據!AO169)</f>
-        <v/>
-      </c>
-      <c r="E168" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E168" s="13">
         <f>IF([1]攻守數據!AP169 = "", "", [1]攻守數據!AP169)</f>
-        <v/>
+        <v>207</v>
       </c>
       <c r="F168" s="13" t="str">
         <f>IF([1]攻守數據!AQ169 = "", "", [1]攻守數據!AQ169)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B169" s="13" t="str">
         <f>IF([1]攻守數據!AM170 = "", "", [1]攻守數據!AM170)</f>
-        <v/>
+        <v>鴨嘴炎獸</v>
       </c>
       <c r="C169" s="13" t="str">
         <f>IF([1]攻守數據!AN170 = "", "", [1]攻守數據!AN170)</f>
-        <v/>
+        <v>格鬥</v>
       </c>
       <c r="D169" s="13" t="str">
         <f>IF([1]攻守數據!AO170 = "", "", [1]攻守數據!AO170)</f>
-        <v/>
-      </c>
-      <c r="E169" s="13" t="str">
+        <v>N</v>
+      </c>
+      <c r="E169" s="13">
         <f>IF([1]攻守數據!AP170 = "", "", [1]攻守數據!AP170)</f>
-        <v/>
+        <v>207</v>
       </c>
       <c r="F169" s="13" t="str">
         <f>IF([1]攻守數據!AQ170 = "", "", [1]攻守數據!AQ170)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B170" s="13" t="str">
         <f>IF([1]攻守數據!AM171 = "", "", [1]攻守數據!AM171)</f>
-        <v/>
+        <v>超甲狂犀</v>
       </c>
       <c r="C170" s="13" t="str">
         <f>IF([1]攻守數據!AN171 = "", "", [1]攻守數據!AN171)</f>
-        <v/>
+        <v>地面</v>
       </c>
       <c r="D170" s="13" t="str">
         <f>IF([1]攻守數據!AO171 = "", "", [1]攻守數據!AO171)</f>
-        <v/>
-      </c>
-      <c r="E170" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E170" s="13">
         <f>IF([1]攻守數據!AP171 = "", "", [1]攻守數據!AP171)</f>
-        <v/>
+        <v>202</v>
       </c>
       <c r="F170" s="13" t="str">
         <f>IF([1]攻守數據!AQ171 = "", "", [1]攻守數據!AQ171)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B171" s="13" t="str">
         <f>IF([1]攻守數據!AM172 = "", "", [1]攻守數據!AM172)</f>
-        <v/>
+        <v>超甲狂犀</v>
       </c>
       <c r="C171" s="13" t="str">
         <f>IF([1]攻守數據!AN172 = "", "", [1]攻守數據!AN172)</f>
-        <v/>
+        <v>岩石</v>
       </c>
       <c r="D171" s="13" t="str">
         <f>IF([1]攻守數據!AO172 = "", "", [1]攻守數據!AO172)</f>
-        <v/>
-      </c>
-      <c r="E171" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E171" s="13">
         <f>IF([1]攻守數據!AP172 = "", "", [1]攻守數據!AP172)</f>
-        <v/>
+        <v>202</v>
       </c>
       <c r="F171" s="13" t="str">
         <f>IF([1]攻守數據!AQ172 = "", "", [1]攻守數據!AQ172)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B172" s="13" t="str">
         <f>IF([1]攻守數據!AM173 = "", "", [1]攻守數據!AM173)</f>
-        <v/>
+        <v>帝牙盧卡</v>
       </c>
       <c r="C172" s="13" t="str">
         <f>IF([1]攻守數據!AN173 = "", "", [1]攻守數據!AN173)</f>
-        <v/>
+        <v>鋼</v>
       </c>
       <c r="D172" s="13" t="str">
         <f>IF([1]攻守數據!AO173 = "", "", [1]攻守數據!AO173)</f>
-        <v/>
-      </c>
-      <c r="E172" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E172" s="13">
         <f>IF([1]攻守數據!AP173 = "", "", [1]攻守數據!AP173)</f>
-        <v/>
+        <v>225</v>
       </c>
       <c r="F172" s="13" t="str">
         <f>IF([1]攻守數據!AQ173 = "", "", [1]攻守數據!AQ173)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B173" s="13" t="str">
         <f>IF([1]攻守數據!AM174 = "", "", [1]攻守數據!AM174)</f>
-        <v/>
+        <v>帝牙盧卡</v>
       </c>
       <c r="C173" s="13" t="str">
         <f>IF([1]攻守數據!AN174 = "", "", [1]攻守數據!AN174)</f>
-        <v/>
+        <v>龍</v>
       </c>
       <c r="D173" s="13" t="str">
         <f>IF([1]攻守數據!AO174 = "", "", [1]攻守數據!AO174)</f>
-        <v/>
-      </c>
-      <c r="E173" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E173" s="13">
         <f>IF([1]攻守數據!AP174 = "", "", [1]攻守數據!AP174)</f>
-        <v/>
+        <v>225</v>
       </c>
       <c r="F173" s="13" t="str">
         <f>IF([1]攻守數據!AQ174 = "", "", [1]攻守數據!AQ174)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B174" s="13" t="str">
         <f>IF([1]攻守數據!AM175 = "", "", [1]攻守數據!AM175)</f>
-        <v/>
+        <v>帕路奇亞</v>
       </c>
       <c r="C174" s="13" t="str">
         <f>IF([1]攻守數據!AN175 = "", "", [1]攻守數據!AN175)</f>
-        <v/>
+        <v>龍</v>
       </c>
       <c r="D174" s="13" t="str">
         <f>IF([1]攻守數據!AO175 = "", "", [1]攻守數據!AO175)</f>
-        <v/>
-      </c>
-      <c r="E174" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E174" s="13">
         <f>IF([1]攻守數據!AP175 = "", "", [1]攻守數據!AP175)</f>
-        <v/>
+        <v>233</v>
       </c>
       <c r="F174" s="13" t="str">
         <f>IF([1]攻守數據!AQ175 = "", "", [1]攻守數據!AQ175)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B175" s="13" t="str">
         <f>IF([1]攻守數據!AM176 = "", "", [1]攻守數據!AM176)</f>
-        <v/>
+        <v>超極巨鋁鋼龍</v>
       </c>
       <c r="C175" s="13" t="str">
         <f>IF([1]攻守數據!AN176 = "", "", [1]攻守數據!AN176)</f>
-        <v/>
+        <v>鋼</v>
       </c>
       <c r="D175" s="13" t="str">
         <f>IF([1]攻守數據!AO176 = "", "", [1]攻守數據!AO176)</f>
-        <v/>
-      </c>
-      <c r="E175" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E175" s="13">
         <f>IF([1]攻守數據!AP176 = "", "", [1]攻守數據!AP176)</f>
-        <v/>
+        <v>201</v>
       </c>
       <c r="F175" s="13" t="str">
         <f>IF([1]攻守數據!AQ176 = "", "", [1]攻守數據!AQ176)</f>
-        <v/>
+        <v>G</v>
       </c>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.3">

--- a/Att.xlsx
+++ b/Att.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\寶可夢\Pokemon_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BB8643-DDF1-4863-A158-CDE2F372B7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35066DD0-B7A1-43F9-AA4C-2B362B723445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1020,7 +1020,7 @@
         </row>
         <row r="43">
           <cell r="AM43" t="str">
-            <v>閃電鳥</v>
+            <v>火焰鳥</v>
           </cell>
           <cell r="AN43" t="str">
             <v>飛行</v>
@@ -1029,7 +1029,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP43">
-            <v>212</v>
+            <v>210</v>
           </cell>
           <cell r="AQ43" t="str">
             <v>D</v>
@@ -1040,7 +1040,7 @@
             <v>火焰鳥</v>
           </cell>
           <cell r="AN44" t="str">
-            <v>飛行</v>
+            <v>火</v>
           </cell>
           <cell r="AO44" t="str">
             <v>Y</v>
@@ -1054,16 +1054,16 @@
         </row>
         <row r="45">
           <cell r="AM45" t="str">
-            <v>火焰鳥</v>
+            <v>藏瑪然特</v>
           </cell>
           <cell r="AN45" t="str">
-            <v>火</v>
+            <v>鋼</v>
           </cell>
           <cell r="AO45" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP45">
-            <v>210</v>
+            <v>218</v>
           </cell>
           <cell r="AQ45" t="str">
             <v>D</v>
@@ -1071,16 +1071,16 @@
         </row>
         <row r="46">
           <cell r="AM46" t="str">
-            <v>藏瑪然特</v>
+            <v>炎帝</v>
           </cell>
           <cell r="AN46" t="str">
-            <v>鋼</v>
+            <v>火</v>
           </cell>
           <cell r="AO46" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP46">
-            <v>218</v>
+            <v>198</v>
           </cell>
           <cell r="AQ46" t="str">
             <v>D</v>
@@ -1088,10 +1088,10 @@
         </row>
         <row r="47">
           <cell r="AM47" t="str">
-            <v>炎帝</v>
+            <v>布莉姆溫</v>
           </cell>
           <cell r="AN47" t="str">
-            <v>火</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO47" t="str">
             <v>Y</v>
@@ -1108,7 +1108,7 @@
             <v>布莉姆溫</v>
           </cell>
           <cell r="AN48" t="str">
-            <v>超能力</v>
+            <v>妖精</v>
           </cell>
           <cell r="AO48" t="str">
             <v>Y</v>
@@ -1122,16 +1122,16 @@
         </row>
         <row r="49">
           <cell r="AM49" t="str">
-            <v>布莉姆溫</v>
+            <v>吼鯨王</v>
           </cell>
           <cell r="AN49" t="str">
-            <v>妖精</v>
+            <v>岩石</v>
           </cell>
           <cell r="AO49" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP49">
-            <v>198</v>
+            <v>147</v>
           </cell>
           <cell r="AQ49" t="str">
             <v>D</v>
@@ -1139,16 +1139,16 @@
         </row>
         <row r="50">
           <cell r="AM50" t="str">
-            <v>吼鯨王</v>
+            <v>拉帝亞斯</v>
           </cell>
           <cell r="AN50" t="str">
-            <v>岩石</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO50" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP50">
-            <v>147</v>
+            <v>190</v>
           </cell>
           <cell r="AQ50" t="str">
             <v>D</v>
@@ -1159,7 +1159,7 @@
             <v>拉帝亞斯</v>
           </cell>
           <cell r="AN51" t="str">
-            <v>超能力</v>
+            <v>龍</v>
           </cell>
           <cell r="AO51" t="str">
             <v>Y</v>
@@ -1173,16 +1173,16 @@
         </row>
         <row r="52">
           <cell r="AM52" t="str">
-            <v>拉帝亞斯</v>
+            <v>高傲雉雞</v>
           </cell>
           <cell r="AN52" t="str">
-            <v>龍</v>
+            <v>飛行</v>
           </cell>
           <cell r="AO52" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP52">
-            <v>190</v>
+            <v>188</v>
           </cell>
           <cell r="AQ52" t="str">
             <v>D</v>
@@ -1190,24 +1190,24 @@
         </row>
         <row r="53">
           <cell r="AM53" t="str">
-            <v>高傲雉雞</v>
+            <v>超極巨巴大蝶</v>
           </cell>
           <cell r="AN53" t="str">
-            <v>飛行</v>
+            <v>蟲</v>
           </cell>
           <cell r="AO53" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP53">
-            <v>188</v>
+            <v>143</v>
           </cell>
           <cell r="AQ53" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="54">
           <cell r="AM54" t="str">
-            <v>超極巨巴大蝶</v>
+            <v>巴大蝶</v>
           </cell>
           <cell r="AN54" t="str">
             <v>蟲</v>
@@ -1219,7 +1219,7 @@
             <v>143</v>
           </cell>
           <cell r="AQ54" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="55">
@@ -1227,10 +1227,10 @@
             <v>巴大蝶</v>
           </cell>
           <cell r="AN55" t="str">
-            <v>蟲</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO55" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP55">
             <v>143</v>
@@ -1241,16 +1241,16 @@
         </row>
         <row r="56">
           <cell r="AM56" t="str">
-            <v>巴大蝶</v>
+            <v>藏飽栗鼠</v>
           </cell>
           <cell r="AN56" t="str">
-            <v>超能力</v>
+            <v>草</v>
           </cell>
           <cell r="AO56" t="str">
             <v>N</v>
           </cell>
           <cell r="AP56">
-            <v>143</v>
+            <v>138</v>
           </cell>
           <cell r="AQ56" t="str">
             <v>D</v>
@@ -1258,16 +1258,16 @@
         </row>
         <row r="57">
           <cell r="AM57" t="str">
-            <v>藏飽栗鼠</v>
+            <v>毛毛角羊</v>
           </cell>
           <cell r="AN57" t="str">
-            <v>草</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AO57" t="str">
             <v>N</v>
           </cell>
           <cell r="AP57">
-            <v>138</v>
+            <v>136</v>
           </cell>
           <cell r="AQ57" t="str">
             <v>D</v>
@@ -1275,24 +1275,24 @@
         </row>
         <row r="58">
           <cell r="AM58" t="str">
-            <v>毛毛角羊</v>
+            <v>超極巨千面避役</v>
           </cell>
           <cell r="AN58" t="str">
-            <v>格鬥</v>
+            <v>水</v>
           </cell>
           <cell r="AO58" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP58">
-            <v>136</v>
+            <v>224</v>
           </cell>
           <cell r="AQ58" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="59">
           <cell r="AM59" t="str">
-            <v>超極巨千面避役</v>
+            <v>千面避役</v>
           </cell>
           <cell r="AN59" t="str">
             <v>水</v>
@@ -1304,12 +1304,12 @@
             <v>224</v>
           </cell>
           <cell r="AQ59" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="60">
           <cell r="AM60" t="str">
-            <v>千面避役</v>
+            <v>超極巨巨鉗蟹</v>
           </cell>
           <cell r="AN60" t="str">
             <v>水</v>
@@ -1318,27 +1318,27 @@
             <v>Y</v>
           </cell>
           <cell r="AP60">
-            <v>224</v>
+            <v>198</v>
           </cell>
           <cell r="AQ60" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="61">
           <cell r="AM61" t="str">
-            <v>超極巨巨鉗蟹</v>
+            <v>巨鉗蟹</v>
           </cell>
           <cell r="AN61" t="str">
-            <v>水</v>
+            <v>地面</v>
           </cell>
           <cell r="AO61" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP61">
             <v>198</v>
           </cell>
           <cell r="AQ61" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="62">
@@ -1346,7 +1346,7 @@
             <v>巨鉗蟹</v>
           </cell>
           <cell r="AN62" t="str">
-            <v>地面</v>
+            <v>鋼</v>
           </cell>
           <cell r="AO62" t="str">
             <v>N</v>
@@ -1360,7 +1360,7 @@
         </row>
         <row r="63">
           <cell r="AM63" t="str">
-            <v>巨鉗蟹</v>
+            <v>高傲雉雞</v>
           </cell>
           <cell r="AN63" t="str">
             <v>鋼</v>
@@ -1369,7 +1369,7 @@
             <v>N</v>
           </cell>
           <cell r="AP63">
-            <v>198</v>
+            <v>188</v>
           </cell>
           <cell r="AQ63" t="str">
             <v>D</v>
@@ -1377,16 +1377,16 @@
         </row>
         <row r="64">
           <cell r="AM64" t="str">
-            <v>高傲雉雞</v>
+            <v>鐮刀盔</v>
           </cell>
           <cell r="AN64" t="str">
-            <v>鋼</v>
+            <v>地面</v>
           </cell>
           <cell r="AO64" t="str">
             <v>N</v>
           </cell>
           <cell r="AP64">
-            <v>188</v>
+            <v>185</v>
           </cell>
           <cell r="AQ64" t="str">
             <v>D</v>
@@ -1397,7 +1397,7 @@
             <v>鐮刀盔</v>
           </cell>
           <cell r="AN65" t="str">
-            <v>地面</v>
+            <v>蟲</v>
           </cell>
           <cell r="AO65" t="str">
             <v>N</v>
@@ -1411,16 +1411,16 @@
         </row>
         <row r="66">
           <cell r="AM66" t="str">
-            <v>鐮刀盔</v>
+            <v>多刺菊石獸</v>
           </cell>
           <cell r="AN66" t="str">
-            <v>蟲</v>
+            <v>地面</v>
           </cell>
           <cell r="AO66" t="str">
             <v>N</v>
           </cell>
           <cell r="AP66">
-            <v>185</v>
+            <v>177</v>
           </cell>
           <cell r="AQ66" t="str">
             <v>D</v>
@@ -1428,16 +1428,16 @@
         </row>
         <row r="67">
           <cell r="AM67" t="str">
-            <v>多刺菊石獸</v>
+            <v>巴大蝶</v>
           </cell>
           <cell r="AN67" t="str">
-            <v>地面</v>
+            <v>蟲</v>
           </cell>
           <cell r="AO67" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP67">
-            <v>177</v>
+            <v>143</v>
           </cell>
           <cell r="AQ67" t="str">
             <v>D</v>
@@ -1445,16 +1445,16 @@
         </row>
         <row r="68">
           <cell r="AM68" t="str">
-            <v>巴大蝶</v>
+            <v>鋼鎧鴉</v>
           </cell>
           <cell r="AN68" t="str">
-            <v>蟲</v>
+            <v>飛行</v>
           </cell>
           <cell r="AO68" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP68">
-            <v>143</v>
+            <v>140</v>
           </cell>
           <cell r="AQ68" t="str">
             <v>D</v>
@@ -1465,7 +1465,7 @@
             <v>鋼鎧鴉</v>
           </cell>
           <cell r="AN69" t="str">
-            <v>飛行</v>
+            <v>鋼</v>
           </cell>
           <cell r="AO69" t="str">
             <v>Y</v>
@@ -1482,10 +1482,10 @@
             <v>鋼鎧鴉</v>
           </cell>
           <cell r="AN70" t="str">
-            <v>鋼</v>
+            <v>地面</v>
           </cell>
           <cell r="AO70" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP70">
             <v>140</v>
@@ -1496,50 +1496,50 @@
         </row>
         <row r="71">
           <cell r="AM71" t="str">
-            <v>鋼鎧鴉</v>
+            <v>超極巨灰塵山</v>
           </cell>
           <cell r="AN71" t="str">
-            <v>地面</v>
+            <v>毒</v>
           </cell>
           <cell r="AO71" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP71">
-            <v>140</v>
+            <v>153</v>
           </cell>
           <cell r="AQ71" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="72">
           <cell r="AM72" t="str">
-            <v>超極巨灰塵山</v>
+            <v>灰塵山</v>
           </cell>
           <cell r="AN72" t="str">
-            <v>毒</v>
+            <v>蟲</v>
           </cell>
           <cell r="AO72" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP72">
             <v>153</v>
           </cell>
           <cell r="AQ72" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="73">
           <cell r="AM73" t="str">
-            <v>灰塵山</v>
+            <v>吼鯨王</v>
           </cell>
           <cell r="AN73" t="str">
-            <v>蟲</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO73" t="str">
             <v>N</v>
           </cell>
           <cell r="AP73">
-            <v>153</v>
+            <v>147</v>
           </cell>
           <cell r="AQ73" t="str">
             <v>D</v>
@@ -1547,24 +1547,24 @@
         </row>
         <row r="74">
           <cell r="AM74" t="str">
-            <v>吼鯨王</v>
+            <v>超極巨水箭龜</v>
           </cell>
           <cell r="AN74" t="str">
-            <v>超能力</v>
+            <v>水</v>
           </cell>
           <cell r="AO74" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP74">
-            <v>147</v>
+            <v>145</v>
           </cell>
           <cell r="AQ74" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="75">
           <cell r="AM75" t="str">
-            <v>超極巨水箭龜</v>
+            <v>水箭龜</v>
           </cell>
           <cell r="AN75" t="str">
             <v>水</v>
@@ -1576,7 +1576,7 @@
             <v>145</v>
           </cell>
           <cell r="AQ75" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="76">
@@ -1584,10 +1584,10 @@
             <v>水箭龜</v>
           </cell>
           <cell r="AN76" t="str">
-            <v>水</v>
+            <v>岩石</v>
           </cell>
           <cell r="AO76" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP76">
             <v>145</v>
@@ -1601,7 +1601,7 @@
             <v>水箭龜</v>
           </cell>
           <cell r="AN77" t="str">
-            <v>岩石</v>
+            <v>惡</v>
           </cell>
           <cell r="AO77" t="str">
             <v>N</v>
@@ -1615,16 +1615,16 @@
         </row>
         <row r="78">
           <cell r="AM78" t="str">
-            <v>水箭龜</v>
+            <v>勾魂眼</v>
           </cell>
           <cell r="AN78" t="str">
-            <v>惡</v>
+            <v>幽靈</v>
           </cell>
           <cell r="AO78" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP78">
-            <v>145</v>
+            <v>121</v>
           </cell>
           <cell r="AQ78" t="str">
             <v>D</v>
@@ -1635,7 +1635,7 @@
             <v>勾魂眼</v>
           </cell>
           <cell r="AN79" t="str">
-            <v>幽靈</v>
+            <v>惡</v>
           </cell>
           <cell r="AO79" t="str">
             <v>Y</v>
@@ -1649,16 +1649,16 @@
         </row>
         <row r="80">
           <cell r="AM80" t="str">
-            <v>勾魂眼</v>
+            <v>鐮刀盔</v>
           </cell>
           <cell r="AN80" t="str">
-            <v>惡</v>
+            <v>水</v>
           </cell>
           <cell r="AO80" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP80">
-            <v>121</v>
+            <v>185</v>
           </cell>
           <cell r="AQ80" t="str">
             <v>D</v>
@@ -1666,16 +1666,16 @@
         </row>
         <row r="81">
           <cell r="AM81" t="str">
-            <v>鐮刀盔</v>
+            <v>藏飽栗鼠</v>
           </cell>
           <cell r="AN81" t="str">
-            <v>水</v>
+            <v>地面</v>
           </cell>
           <cell r="AO81" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP81">
-            <v>185</v>
+            <v>138</v>
           </cell>
           <cell r="AQ81" t="str">
             <v>D</v>
@@ -1686,7 +1686,7 @@
             <v>藏飽栗鼠</v>
           </cell>
           <cell r="AN82" t="str">
-            <v>地面</v>
+            <v>惡</v>
           </cell>
           <cell r="AO82" t="str">
             <v>N</v>
@@ -1700,16 +1700,16 @@
         </row>
         <row r="83">
           <cell r="AM83" t="str">
-            <v>藏飽栗鼠</v>
+            <v>多刺菊石獸</v>
           </cell>
           <cell r="AN83" t="str">
-            <v>惡</v>
+            <v>水</v>
           </cell>
           <cell r="AO83" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP83">
-            <v>138</v>
+            <v>177</v>
           </cell>
           <cell r="AQ83" t="str">
             <v>D</v>
@@ -1717,7 +1717,7 @@
         </row>
         <row r="84">
           <cell r="AM84" t="str">
-            <v>多刺菊石獸</v>
+            <v>水君</v>
           </cell>
           <cell r="AN84" t="str">
             <v>水</v>
@@ -1726,7 +1726,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP84">
-            <v>177</v>
+            <v>154</v>
           </cell>
           <cell r="AQ84" t="str">
             <v>D</v>
@@ -1734,7 +1734,7 @@
         </row>
         <row r="85">
           <cell r="AM85" t="str">
-            <v>水君</v>
+            <v>吼鯨王</v>
           </cell>
           <cell r="AN85" t="str">
             <v>水</v>
@@ -1743,7 +1743,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP85">
-            <v>154</v>
+            <v>147</v>
           </cell>
           <cell r="AQ85" t="str">
             <v>D</v>
@@ -1751,16 +1751,16 @@
         </row>
         <row r="86">
           <cell r="AM86" t="str">
-            <v>吼鯨王</v>
+            <v>幸福蛋</v>
           </cell>
           <cell r="AN86" t="str">
-            <v>水</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO86" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP86">
-            <v>147</v>
+            <v>113</v>
           </cell>
           <cell r="AQ86" t="str">
             <v>D</v>
@@ -1768,16 +1768,16 @@
         </row>
         <row r="87">
           <cell r="AM87" t="str">
-            <v>幸福蛋</v>
+            <v>急凍鳥</v>
           </cell>
           <cell r="AN87" t="str">
-            <v>超能力</v>
+            <v>冰</v>
           </cell>
           <cell r="AO87" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP87">
-            <v>113</v>
+            <v>164</v>
           </cell>
           <cell r="AQ87" t="str">
             <v>D</v>
@@ -1785,7 +1785,7 @@
         </row>
         <row r="88">
           <cell r="AM88" t="str">
-            <v>急凍鳥</v>
+            <v>幾何雪花</v>
           </cell>
           <cell r="AN88" t="str">
             <v>冰</v>
@@ -1794,7 +1794,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP88">
-            <v>164</v>
+            <v>162</v>
           </cell>
           <cell r="AQ88" t="str">
             <v>D</v>
@@ -1802,16 +1802,16 @@
         </row>
         <row r="89">
           <cell r="AM89" t="str">
-            <v>幾何雪花</v>
+            <v>壺壺</v>
           </cell>
           <cell r="AN89" t="str">
-            <v>冰</v>
+            <v>岩石</v>
           </cell>
           <cell r="AO89" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP89">
-            <v>162</v>
+            <v>17</v>
           </cell>
           <cell r="AQ89" t="str">
             <v>D</v>
@@ -1822,7 +1822,7 @@
             <v>壺壺</v>
           </cell>
           <cell r="AN90" t="str">
-            <v>岩石</v>
+            <v>蟲</v>
           </cell>
           <cell r="AO90" t="str">
             <v>Y</v>
@@ -1836,16 +1836,16 @@
         </row>
         <row r="91">
           <cell r="AM91" t="str">
-            <v>壺壺</v>
+            <v>胡地</v>
           </cell>
           <cell r="AN91" t="str">
-            <v>蟲</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO91" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP91">
-            <v>17</v>
+            <v>225</v>
           </cell>
           <cell r="AQ91" t="str">
             <v>D</v>
@@ -1856,10 +1856,10 @@
             <v>胡地</v>
           </cell>
           <cell r="AN92" t="str">
-            <v>超能力</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AO92" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP92">
             <v>225</v>
@@ -1870,36 +1870,36 @@
         </row>
         <row r="93">
           <cell r="AM93" t="str">
-            <v>胡地</v>
+            <v>超極巨拉普拉斯</v>
           </cell>
           <cell r="AN93" t="str">
-            <v>格鬥</v>
+            <v>冰</v>
           </cell>
           <cell r="AO93" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP93">
-            <v>225</v>
+            <v>141</v>
           </cell>
           <cell r="AQ93" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="94">
           <cell r="AM94" t="str">
-            <v>超極巨拉普拉斯</v>
+            <v>鋁鋼龍</v>
           </cell>
           <cell r="AN94" t="str">
-            <v>冰</v>
+            <v>鋼</v>
           </cell>
           <cell r="AO94" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP94">
-            <v>141</v>
+            <v>201</v>
           </cell>
           <cell r="AQ94" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="95">
@@ -1907,7 +1907,7 @@
             <v>鋁鋼龍</v>
           </cell>
           <cell r="AN95" t="str">
-            <v>鋼</v>
+            <v>龍</v>
           </cell>
           <cell r="AO95" t="str">
             <v>Y</v>
@@ -1924,10 +1924,10 @@
             <v>鋁鋼龍</v>
           </cell>
           <cell r="AN96" t="str">
-            <v>龍</v>
+            <v>一般</v>
           </cell>
           <cell r="AO96" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP96">
             <v>201</v>
@@ -1938,16 +1938,16 @@
         </row>
         <row r="97">
           <cell r="AM97" t="str">
-            <v>鋁鋼龍</v>
+            <v>巨金怪</v>
           </cell>
           <cell r="AN97" t="str">
-            <v>一般</v>
+            <v>幽靈</v>
           </cell>
           <cell r="AO97" t="str">
             <v>N</v>
           </cell>
           <cell r="AP97">
-            <v>201</v>
+            <v>214</v>
           </cell>
           <cell r="AQ97" t="str">
             <v>D</v>
@@ -1955,16 +1955,16 @@
         </row>
         <row r="98">
           <cell r="AM98" t="str">
-            <v>巨金怪</v>
+            <v>沙奈朵</v>
           </cell>
           <cell r="AN98" t="str">
-            <v>幽靈</v>
+            <v>妖精</v>
           </cell>
           <cell r="AO98" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP98">
-            <v>214</v>
+            <v>199</v>
           </cell>
           <cell r="AQ98" t="str">
             <v>D</v>
@@ -1975,7 +1975,7 @@
             <v>沙奈朵</v>
           </cell>
           <cell r="AN99" t="str">
-            <v>妖精</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO99" t="str">
             <v>Y</v>
@@ -1992,10 +1992,10 @@
             <v>沙奈朵</v>
           </cell>
           <cell r="AN100" t="str">
-            <v>超能力</v>
+            <v>草</v>
           </cell>
           <cell r="AO100" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP100">
             <v>199</v>
@@ -2009,7 +2009,7 @@
             <v>沙奈朵</v>
           </cell>
           <cell r="AN101" t="str">
-            <v>草</v>
+            <v>電</v>
           </cell>
           <cell r="AO101" t="str">
             <v>N</v>
@@ -2023,16 +2023,16 @@
         </row>
         <row r="102">
           <cell r="AM102" t="str">
-            <v>沙奈朵</v>
+            <v>甜冷美后</v>
           </cell>
           <cell r="AN102" t="str">
-            <v>電</v>
+            <v>草</v>
           </cell>
           <cell r="AO102" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP102">
-            <v>199</v>
+            <v>187</v>
           </cell>
           <cell r="AQ102" t="str">
             <v>D</v>
@@ -2043,10 +2043,10 @@
             <v>甜冷美后</v>
           </cell>
           <cell r="AN103" t="str">
-            <v>草</v>
+            <v>妖精</v>
           </cell>
           <cell r="AO103" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP103">
             <v>187</v>
@@ -2057,50 +2057,50 @@
         </row>
         <row r="104">
           <cell r="AM104" t="str">
-            <v>甜冷美后</v>
+            <v>超極巨伊布</v>
           </cell>
           <cell r="AN104" t="str">
-            <v>妖精</v>
+            <v>一般</v>
           </cell>
           <cell r="AO104" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP104">
-            <v>187</v>
+            <v>94</v>
           </cell>
           <cell r="AQ104" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="105">
           <cell r="AM105" t="str">
-            <v>超極巨伊布</v>
+            <v>水伊布</v>
           </cell>
           <cell r="AN105" t="str">
-            <v>一般</v>
+            <v>水</v>
           </cell>
           <cell r="AO105" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP105">
-            <v>94</v>
+            <v>174</v>
           </cell>
           <cell r="AQ105" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="106">
           <cell r="AM106" t="str">
-            <v>水伊布</v>
+            <v>雷伊布</v>
           </cell>
           <cell r="AN106" t="str">
-            <v>水</v>
+            <v>電</v>
           </cell>
           <cell r="AO106" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP106">
-            <v>174</v>
+            <v>195</v>
           </cell>
           <cell r="AQ106" t="str">
             <v>D</v>
@@ -2108,16 +2108,16 @@
         </row>
         <row r="107">
           <cell r="AM107" t="str">
-            <v>雷伊布</v>
+            <v>火伊布</v>
           </cell>
           <cell r="AN107" t="str">
-            <v>電</v>
+            <v>火</v>
           </cell>
           <cell r="AO107" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP107">
-            <v>195</v>
+            <v>206</v>
           </cell>
           <cell r="AQ107" t="str">
             <v>D</v>
@@ -2125,16 +2125,16 @@
         </row>
         <row r="108">
           <cell r="AM108" t="str">
-            <v>火伊布</v>
+            <v>太陽伊布</v>
           </cell>
           <cell r="AN108" t="str">
-            <v>火</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO108" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP108">
-            <v>206</v>
+            <v>218</v>
           </cell>
           <cell r="AQ108" t="str">
             <v>D</v>
@@ -2142,16 +2142,16 @@
         </row>
         <row r="109">
           <cell r="AM109" t="str">
-            <v>太陽伊布</v>
+            <v>月亮伊布</v>
           </cell>
           <cell r="AN109" t="str">
-            <v>超能力</v>
+            <v>惡</v>
           </cell>
           <cell r="AO109" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP109">
-            <v>218</v>
+            <v>111</v>
           </cell>
           <cell r="AQ109" t="str">
             <v>D</v>
@@ -2159,16 +2159,16 @@
         </row>
         <row r="110">
           <cell r="AM110" t="str">
-            <v>月亮伊布</v>
+            <v>葉伊布</v>
           </cell>
           <cell r="AN110" t="str">
-            <v>惡</v>
+            <v>草</v>
           </cell>
           <cell r="AO110" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP110">
-            <v>111</v>
+            <v>183</v>
           </cell>
           <cell r="AQ110" t="str">
             <v>D</v>
@@ -2176,16 +2176,16 @@
         </row>
         <row r="111">
           <cell r="AM111" t="str">
-            <v>葉伊布</v>
+            <v>冰伊布</v>
           </cell>
           <cell r="AN111" t="str">
-            <v>草</v>
+            <v>冰</v>
           </cell>
           <cell r="AO111" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP111">
-            <v>183</v>
+            <v>200</v>
           </cell>
           <cell r="AQ111" t="str">
             <v>D</v>
@@ -2193,16 +2193,16 @@
         </row>
         <row r="112">
           <cell r="AM112" t="str">
-            <v>冰伊布</v>
+            <v>仙子伊布</v>
           </cell>
           <cell r="AN112" t="str">
-            <v>冰</v>
+            <v>妖精</v>
           </cell>
           <cell r="AO112" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP112">
-            <v>200</v>
+            <v>172</v>
           </cell>
           <cell r="AQ112" t="str">
             <v>D</v>
@@ -2210,16 +2210,16 @@
         </row>
         <row r="113">
           <cell r="AM113" t="str">
-            <v>仙子伊布</v>
+            <v>艾路雷朵</v>
           </cell>
           <cell r="AN113" t="str">
-            <v>妖精</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AO113" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP113">
-            <v>172</v>
+            <v>199</v>
           </cell>
           <cell r="AQ113" t="str">
             <v>D</v>
@@ -2230,7 +2230,7 @@
             <v>艾路雷朵</v>
           </cell>
           <cell r="AN114" t="str">
-            <v>格鬥</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO114" t="str">
             <v>Y</v>
@@ -2247,10 +2247,10 @@
             <v>艾路雷朵</v>
           </cell>
           <cell r="AN115" t="str">
-            <v>超能力</v>
+            <v>妖精</v>
           </cell>
           <cell r="AO115" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP115">
             <v>199</v>
@@ -2261,16 +2261,16 @@
         </row>
         <row r="116">
           <cell r="AM116" t="str">
-            <v>艾路雷朵</v>
+            <v>烏賊王</v>
           </cell>
           <cell r="AN116" t="str">
-            <v>妖精</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO116" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP116">
-            <v>199</v>
+            <v>151</v>
           </cell>
           <cell r="AQ116" t="str">
             <v>D</v>
@@ -2281,10 +2281,10 @@
             <v>烏賊王</v>
           </cell>
           <cell r="AN117" t="str">
-            <v>超能力</v>
+            <v>飛行</v>
           </cell>
           <cell r="AO117" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP117">
             <v>151</v>
@@ -2295,16 +2295,16 @@
         </row>
         <row r="118">
           <cell r="AM118" t="str">
-            <v>烏賊王</v>
+            <v>洛奇亞</v>
           </cell>
           <cell r="AN118" t="str">
-            <v>飛行</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO118" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP118">
-            <v>151</v>
+            <v>164</v>
           </cell>
           <cell r="AQ118" t="str">
             <v>D</v>
@@ -2315,10 +2315,10 @@
             <v>洛奇亞</v>
           </cell>
           <cell r="AN119" t="str">
-            <v>超能力</v>
+            <v>龍</v>
           </cell>
           <cell r="AO119" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP119">
             <v>164</v>
@@ -2329,16 +2329,16 @@
         </row>
         <row r="120">
           <cell r="AM120" t="str">
-            <v>洛奇亞</v>
+            <v>飛腿郎</v>
           </cell>
           <cell r="AN120" t="str">
-            <v>龍</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AO120" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP120">
-            <v>164</v>
+            <v>189</v>
           </cell>
           <cell r="AQ120" t="str">
             <v>D</v>
@@ -2346,7 +2346,7 @@
         </row>
         <row r="121">
           <cell r="AM121" t="str">
-            <v>飛腿郎</v>
+            <v>快拳郎</v>
           </cell>
           <cell r="AN121" t="str">
             <v>格鬥</v>
@@ -2355,7 +2355,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP121">
-            <v>189</v>
+            <v>164</v>
           </cell>
           <cell r="AQ121" t="str">
             <v>D</v>
@@ -2366,10 +2366,10 @@
             <v>快拳郎</v>
           </cell>
           <cell r="AN122" t="str">
-            <v>格鬥</v>
+            <v>鋼</v>
           </cell>
           <cell r="AO122" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP122">
             <v>164</v>
@@ -2380,16 +2380,16 @@
         </row>
         <row r="123">
           <cell r="AM123" t="str">
-            <v>快拳郎</v>
+            <v>帝牙海獅</v>
           </cell>
           <cell r="AN123" t="str">
-            <v>鋼</v>
+            <v>冰</v>
           </cell>
           <cell r="AO123" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP123">
-            <v>164</v>
+            <v>156</v>
           </cell>
           <cell r="AQ123" t="str">
             <v>D</v>
@@ -2397,16 +2397,16 @@
         </row>
         <row r="124">
           <cell r="AM124" t="str">
-            <v>帝牙海獅</v>
+            <v>龐岩怪</v>
           </cell>
           <cell r="AN124" t="str">
-            <v>水</v>
+            <v>岩石</v>
           </cell>
           <cell r="AO124" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP124">
-            <v>156</v>
+            <v>190</v>
           </cell>
           <cell r="AQ124" t="str">
             <v>D</v>
@@ -2414,16 +2414,16 @@
         </row>
         <row r="125">
           <cell r="AM125" t="str">
-            <v>帝牙海獅</v>
+            <v>龐岩怪</v>
           </cell>
           <cell r="AN125" t="str">
-            <v>冰</v>
+            <v>地面</v>
           </cell>
           <cell r="AO125" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP125">
-            <v>156</v>
+            <v>190</v>
           </cell>
           <cell r="AQ125" t="str">
             <v>D</v>
@@ -2431,16 +2431,16 @@
         </row>
         <row r="126">
           <cell r="AM126" t="str">
-            <v>龐岩怪</v>
+            <v>老翁龍</v>
           </cell>
           <cell r="AN126" t="str">
-            <v>岩石</v>
+            <v>龍</v>
           </cell>
           <cell r="AO126" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP126">
-            <v>190</v>
+            <v>194</v>
           </cell>
           <cell r="AQ126" t="str">
             <v>D</v>
@@ -2448,16 +2448,16 @@
         </row>
         <row r="127">
           <cell r="AM127" t="str">
-            <v>龐岩怪</v>
+            <v>老翁龍</v>
           </cell>
           <cell r="AN127" t="str">
-            <v>地面</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO127" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP127">
-            <v>190</v>
+            <v>194</v>
           </cell>
           <cell r="AQ127" t="str">
             <v>D</v>
@@ -2465,16 +2465,16 @@
         </row>
         <row r="128">
           <cell r="AM128" t="str">
-            <v>老翁龍</v>
+            <v>鳳王</v>
           </cell>
           <cell r="AN128" t="str">
-            <v>龍</v>
+            <v>火</v>
           </cell>
           <cell r="AO128" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP128">
-            <v>194</v>
+            <v>201</v>
           </cell>
           <cell r="AQ128" t="str">
             <v>D</v>
@@ -2482,16 +2482,16 @@
         </row>
         <row r="129">
           <cell r="AM129" t="str">
-            <v>老翁龍</v>
+            <v>鳳王</v>
           </cell>
           <cell r="AN129" t="str">
             <v>超能力</v>
           </cell>
           <cell r="AO129" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP129">
-            <v>194</v>
+            <v>201</v>
           </cell>
           <cell r="AQ129" t="str">
             <v>D</v>
@@ -2502,10 +2502,10 @@
             <v>鳳王</v>
           </cell>
           <cell r="AN130" t="str">
-            <v>火</v>
+            <v>一般</v>
           </cell>
           <cell r="AO130" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP130">
             <v>201</v>
@@ -2519,7 +2519,7 @@
             <v>鳳王</v>
           </cell>
           <cell r="AN131" t="str">
-            <v>超能力</v>
+            <v>鋼</v>
           </cell>
           <cell r="AO131" t="str">
             <v>N</v>
@@ -2533,16 +2533,16 @@
         </row>
         <row r="132">
           <cell r="AM132" t="str">
-            <v>鳳王</v>
+            <v>風速狗</v>
           </cell>
           <cell r="AN132" t="str">
-            <v>一般</v>
+            <v>火</v>
           </cell>
           <cell r="AO132" t="str">
             <v>N</v>
           </cell>
           <cell r="AP132">
-            <v>201</v>
+            <v>191</v>
           </cell>
           <cell r="AQ132" t="str">
             <v>D</v>
@@ -2550,16 +2550,16 @@
         </row>
         <row r="133">
           <cell r="AM133" t="str">
-            <v>鳳王</v>
+            <v>風速狗</v>
           </cell>
           <cell r="AN133" t="str">
-            <v>鋼</v>
+            <v>惡</v>
           </cell>
           <cell r="AO133" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP133">
-            <v>201</v>
+            <v>191</v>
           </cell>
           <cell r="AQ133" t="str">
             <v>D</v>
@@ -2570,10 +2570,10 @@
             <v>風速狗</v>
           </cell>
           <cell r="AN134" t="str">
-            <v>火</v>
+            <v>電</v>
           </cell>
           <cell r="AO134" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP134">
             <v>191</v>
@@ -2584,16 +2584,16 @@
         </row>
         <row r="135">
           <cell r="AM135" t="str">
-            <v>風速狗</v>
+            <v>喵喵</v>
           </cell>
           <cell r="AN135" t="str">
-            <v>惡</v>
+            <v>一般</v>
           </cell>
           <cell r="AO135" t="str">
             <v>N</v>
           </cell>
           <cell r="AP135">
-            <v>191</v>
+            <v>85</v>
           </cell>
           <cell r="AQ135" t="str">
             <v>D</v>
@@ -2601,33 +2601,33 @@
         </row>
         <row r="136">
           <cell r="AM136" t="str">
-            <v>風速狗</v>
+            <v>超極巨喵喵</v>
           </cell>
           <cell r="AN136" t="str">
             <v>電</v>
           </cell>
           <cell r="AO136" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP136">
-            <v>191</v>
+            <v>85</v>
           </cell>
           <cell r="AQ136" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="137">
           <cell r="AM137" t="str">
-            <v>超極巨喵喵</v>
+            <v>超極巨皮卡丘</v>
           </cell>
           <cell r="AN137" t="str">
-            <v>一般</v>
+            <v>電</v>
           </cell>
           <cell r="AO137" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP137">
-            <v>85</v>
+            <v>100</v>
           </cell>
           <cell r="AQ137" t="str">
             <v>G</v>
@@ -2635,33 +2635,33 @@
         </row>
         <row r="138">
           <cell r="AM138" t="str">
-            <v>超極巨皮卡丘</v>
+            <v>雷丘</v>
           </cell>
           <cell r="AN138" t="str">
-            <v>電</v>
+            <v>妖精</v>
           </cell>
           <cell r="AO138" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP138">
-            <v>100</v>
+            <v>164</v>
           </cell>
           <cell r="AQ138" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="139">
           <cell r="AM139" t="str">
-            <v>雷丘</v>
+            <v>雷吉艾斯</v>
           </cell>
           <cell r="AN139" t="str">
-            <v>電</v>
+            <v>冰</v>
           </cell>
           <cell r="AO139" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP139">
-            <v>164</v>
+            <v>153</v>
           </cell>
           <cell r="AQ139" t="str">
             <v>D</v>
@@ -2669,16 +2669,16 @@
         </row>
         <row r="140">
           <cell r="AM140" t="str">
-            <v>雷丘</v>
+            <v>雷吉艾斯</v>
           </cell>
           <cell r="AN140" t="str">
-            <v>妖精</v>
+            <v>一般</v>
           </cell>
           <cell r="AO140" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP140">
-            <v>164</v>
+            <v>153</v>
           </cell>
           <cell r="AQ140" t="str">
             <v>D</v>
@@ -2689,10 +2689,10 @@
             <v>雷吉艾斯</v>
           </cell>
           <cell r="AN141" t="str">
-            <v>冰</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AO141" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP141">
             <v>153</v>
@@ -2703,16 +2703,16 @@
         </row>
         <row r="142">
           <cell r="AM142" t="str">
-            <v>雷吉艾斯</v>
+            <v>沙漠蜻蜓</v>
           </cell>
           <cell r="AN142" t="str">
-            <v>一般</v>
+            <v>地面</v>
           </cell>
           <cell r="AO142" t="str">
             <v>N</v>
           </cell>
           <cell r="AP142">
-            <v>153</v>
+            <v>174</v>
           </cell>
           <cell r="AQ142" t="str">
             <v>D</v>
@@ -2720,16 +2720,16 @@
         </row>
         <row r="143">
           <cell r="AM143" t="str">
-            <v>雷吉艾斯</v>
+            <v>沙漠蜻蜓</v>
           </cell>
           <cell r="AN143" t="str">
-            <v>格鬥</v>
+            <v>龍</v>
           </cell>
           <cell r="AO143" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP143">
-            <v>153</v>
+            <v>174</v>
           </cell>
           <cell r="AQ143" t="str">
             <v>D</v>
@@ -2737,16 +2737,16 @@
         </row>
         <row r="144">
           <cell r="AM144" t="str">
-            <v>沙漠蜻蜓</v>
+            <v>雷吉洛克</v>
           </cell>
           <cell r="AN144" t="str">
-            <v>地面</v>
+            <v>岩石</v>
           </cell>
           <cell r="AO144" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP144">
-            <v>174</v>
+            <v>153</v>
           </cell>
           <cell r="AQ144" t="str">
             <v>D</v>
@@ -2754,16 +2754,16 @@
         </row>
         <row r="145">
           <cell r="AM145" t="str">
-            <v>沙漠蜻蜓</v>
+            <v>雷吉洛克</v>
           </cell>
           <cell r="AN145" t="str">
-            <v>龍</v>
+            <v>一般</v>
           </cell>
           <cell r="AO145" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP145">
-            <v>174</v>
+            <v>153</v>
           </cell>
           <cell r="AQ145" t="str">
             <v>D</v>
@@ -2774,10 +2774,10 @@
             <v>雷吉洛克</v>
           </cell>
           <cell r="AN146" t="str">
-            <v>岩石</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AO146" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP146">
             <v>153</v>
@@ -2788,16 +2788,16 @@
         </row>
         <row r="147">
           <cell r="AM147" t="str">
-            <v>雷吉洛克</v>
+            <v>雷吉斯奇魯</v>
           </cell>
           <cell r="AN147" t="str">
-            <v>一般</v>
+            <v>鋼</v>
           </cell>
           <cell r="AO147" t="str">
             <v>N</v>
           </cell>
           <cell r="AP147">
-            <v>153</v>
+            <v>125</v>
           </cell>
           <cell r="AQ147" t="str">
             <v>D</v>
@@ -2805,16 +2805,16 @@
         </row>
         <row r="148">
           <cell r="AM148" t="str">
-            <v>雷吉洛克</v>
+            <v>雷吉斯奇魯</v>
           </cell>
           <cell r="AN148" t="str">
-            <v>格鬥</v>
+            <v>一般</v>
           </cell>
           <cell r="AO148" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP148">
-            <v>153</v>
+            <v>125</v>
           </cell>
           <cell r="AQ148" t="str">
             <v>D</v>
@@ -2825,10 +2825,10 @@
             <v>雷吉斯奇魯</v>
           </cell>
           <cell r="AN149" t="str">
-            <v>鋼</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AO149" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP149">
             <v>125</v>
@@ -2839,16 +2839,16 @@
         </row>
         <row r="150">
           <cell r="AM150" t="str">
-            <v>雷吉斯奇魯</v>
+            <v>長毛巨魔</v>
           </cell>
           <cell r="AN150" t="str">
-            <v>一般</v>
+            <v>惡</v>
           </cell>
           <cell r="AO150" t="str">
             <v>N</v>
           </cell>
           <cell r="AP150">
-            <v>125</v>
+            <v>191</v>
           </cell>
           <cell r="AQ150" t="str">
             <v>D</v>
@@ -2856,50 +2856,50 @@
         </row>
         <row r="151">
           <cell r="AM151" t="str">
-            <v>雷吉斯奇魯</v>
+            <v>超極巨長毛巨魔</v>
           </cell>
           <cell r="AN151" t="str">
-            <v>格鬥</v>
+            <v>草</v>
           </cell>
           <cell r="AO151" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP151">
-            <v>125</v>
+            <v>191</v>
           </cell>
           <cell r="AQ151" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="152">
           <cell r="AM152" t="str">
-            <v>超極巨長毛巨魔</v>
+            <v>風妖精</v>
           </cell>
           <cell r="AN152" t="str">
-            <v>惡</v>
+            <v>妖精</v>
           </cell>
           <cell r="AO152" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP152">
-            <v>191</v>
+            <v>141</v>
           </cell>
           <cell r="AQ152" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="153">
           <cell r="AM153" t="str">
-            <v>風妖精</v>
+            <v>蜂女王</v>
           </cell>
           <cell r="AN153" t="str">
-            <v>草</v>
+            <v>蟲</v>
           </cell>
           <cell r="AO153" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP153">
-            <v>141</v>
+            <v>130</v>
           </cell>
           <cell r="AQ153" t="str">
             <v>D</v>
@@ -2907,16 +2907,16 @@
         </row>
         <row r="154">
           <cell r="AM154" t="str">
-            <v>風妖精</v>
+            <v>蜂女王</v>
           </cell>
           <cell r="AN154" t="str">
-            <v>妖精</v>
+            <v>飛行</v>
           </cell>
           <cell r="AO154" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP154">
-            <v>141</v>
+            <v>130</v>
           </cell>
           <cell r="AQ154" t="str">
             <v>D</v>
@@ -2927,7 +2927,7 @@
             <v>蜂女王</v>
           </cell>
           <cell r="AN155" t="str">
-            <v>蟲</v>
+            <v>毒</v>
           </cell>
           <cell r="AO155" t="str">
             <v>Y</v>
@@ -2941,16 +2941,16 @@
         </row>
         <row r="156">
           <cell r="AM156" t="str">
-            <v>蜂女王</v>
+            <v>電擊魔獸</v>
           </cell>
           <cell r="AN156" t="str">
-            <v>飛行</v>
+            <v>電</v>
           </cell>
           <cell r="AO156" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP156">
-            <v>130</v>
+            <v>209</v>
           </cell>
           <cell r="AQ156" t="str">
             <v>D</v>
@@ -2958,16 +2958,16 @@
         </row>
         <row r="157">
           <cell r="AM157" t="str">
-            <v>蜂女王</v>
+            <v>電擊魔獸</v>
           </cell>
           <cell r="AN157" t="str">
-            <v>毒</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AO157" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP157">
-            <v>130</v>
+            <v>209</v>
           </cell>
           <cell r="AQ157" t="str">
             <v>D</v>
@@ -2975,16 +2975,16 @@
         </row>
         <row r="158">
           <cell r="AM158" t="str">
-            <v>電擊魔獸</v>
+            <v>貓頭夜鷹</v>
           </cell>
           <cell r="AN158" t="str">
-            <v>電</v>
+            <v>飛行</v>
           </cell>
           <cell r="AO158" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP158">
-            <v>209</v>
+            <v>126</v>
           </cell>
           <cell r="AQ158" t="str">
             <v>D</v>
@@ -2992,16 +2992,16 @@
         </row>
         <row r="159">
           <cell r="AM159" t="str">
-            <v>電擊魔獸</v>
+            <v>貓頭夜鷹</v>
           </cell>
           <cell r="AN159" t="str">
-            <v>格鬥</v>
+            <v>超能力</v>
           </cell>
           <cell r="AO159" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP159">
-            <v>209</v>
+            <v>126</v>
           </cell>
           <cell r="AQ159" t="str">
             <v>D</v>
@@ -3009,16 +3009,16 @@
         </row>
         <row r="160">
           <cell r="AM160" t="str">
-            <v>貓頭夜鷹</v>
+            <v>暴鯉龍</v>
           </cell>
           <cell r="AN160" t="str">
-            <v>飛行</v>
+            <v>水</v>
           </cell>
           <cell r="AO160" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP160">
-            <v>126</v>
+            <v>199</v>
           </cell>
           <cell r="AQ160" t="str">
             <v>D</v>
@@ -3026,16 +3026,16 @@
         </row>
         <row r="161">
           <cell r="AM161" t="str">
-            <v>貓頭夜鷹</v>
+            <v>暴鯉龍</v>
           </cell>
           <cell r="AN161" t="str">
-            <v>超能力</v>
+            <v>惡</v>
           </cell>
           <cell r="AO161" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP161">
-            <v>126</v>
+            <v>199</v>
           </cell>
           <cell r="AQ161" t="str">
             <v>D</v>
@@ -3046,7 +3046,7 @@
             <v>暴鯉龍</v>
           </cell>
           <cell r="AN162" t="str">
-            <v>水</v>
+            <v>龍</v>
           </cell>
           <cell r="AO162" t="str">
             <v>Y</v>
@@ -3060,16 +3060,16 @@
         </row>
         <row r="163">
           <cell r="AM163" t="str">
-            <v>暴鯉龍</v>
+            <v>三首惡龍</v>
           </cell>
           <cell r="AN163" t="str">
             <v>惡</v>
           </cell>
           <cell r="AO163" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP163">
-            <v>199</v>
+            <v>214</v>
           </cell>
           <cell r="AQ163" t="str">
             <v>D</v>
@@ -3077,16 +3077,16 @@
         </row>
         <row r="164">
           <cell r="AM164" t="str">
-            <v>暴鯉龍</v>
+            <v>三首惡龍</v>
           </cell>
           <cell r="AN164" t="str">
             <v>龍</v>
           </cell>
           <cell r="AO164" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP164">
-            <v>199</v>
+            <v>214</v>
           </cell>
           <cell r="AQ164" t="str">
             <v>D</v>
@@ -3094,16 +3094,16 @@
         </row>
         <row r="165">
           <cell r="AM165" t="str">
-            <v>三首惡龍</v>
+            <v>美納斯</v>
           </cell>
           <cell r="AN165" t="str">
-            <v>惡</v>
+            <v>水</v>
           </cell>
           <cell r="AO165" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP165">
-            <v>214</v>
+            <v>164</v>
           </cell>
           <cell r="AQ165" t="str">
             <v>D</v>
@@ -3111,7 +3111,7 @@
         </row>
         <row r="166">
           <cell r="AM166" t="str">
-            <v>三首惡龍</v>
+            <v>美納斯</v>
           </cell>
           <cell r="AN166" t="str">
             <v>龍</v>
@@ -3120,7 +3120,7 @@
             <v>Y</v>
           </cell>
           <cell r="AP166">
-            <v>214</v>
+            <v>164</v>
           </cell>
           <cell r="AQ166" t="str">
             <v>D</v>
@@ -3128,16 +3128,16 @@
         </row>
         <row r="167">
           <cell r="AM167" t="str">
-            <v>美納斯</v>
+            <v>鴨嘴炎獸</v>
           </cell>
           <cell r="AN167" t="str">
-            <v>水</v>
+            <v>火</v>
           </cell>
           <cell r="AO167" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP167">
-            <v>164</v>
+            <v>207</v>
           </cell>
           <cell r="AQ167" t="str">
             <v>D</v>
@@ -3145,16 +3145,16 @@
         </row>
         <row r="168">
           <cell r="AM168" t="str">
-            <v>美納斯</v>
+            <v>鴨嘴炎獸</v>
           </cell>
           <cell r="AN168" t="str">
-            <v>龍</v>
+            <v>格鬥</v>
           </cell>
           <cell r="AO168" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP168">
-            <v>164</v>
+            <v>207</v>
           </cell>
           <cell r="AQ168" t="str">
             <v>D</v>
@@ -3162,16 +3162,16 @@
         </row>
         <row r="169">
           <cell r="AM169" t="str">
-            <v>鴨嘴炎獸</v>
+            <v>超甲狂犀</v>
           </cell>
           <cell r="AN169" t="str">
-            <v>火</v>
+            <v>地面</v>
           </cell>
           <cell r="AO169" t="str">
-            <v>Y</v>
+            <v>N</v>
           </cell>
           <cell r="AP169">
-            <v>207</v>
+            <v>202</v>
           </cell>
           <cell r="AQ169" t="str">
             <v>D</v>
@@ -3179,16 +3179,16 @@
         </row>
         <row r="170">
           <cell r="AM170" t="str">
-            <v>鴨嘴炎獸</v>
+            <v>超甲狂犀</v>
           </cell>
           <cell r="AN170" t="str">
-            <v>格鬥</v>
+            <v>岩石</v>
           </cell>
           <cell r="AO170" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP170">
-            <v>207</v>
+            <v>202</v>
           </cell>
           <cell r="AQ170" t="str">
             <v>D</v>
@@ -3196,16 +3196,16 @@
         </row>
         <row r="171">
           <cell r="AM171" t="str">
-            <v>超甲狂犀</v>
+            <v>帝牙盧卡</v>
           </cell>
           <cell r="AN171" t="str">
-            <v>地面</v>
+            <v>鋼</v>
           </cell>
           <cell r="AO171" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP171">
-            <v>202</v>
+            <v>225</v>
           </cell>
           <cell r="AQ171" t="str">
             <v>D</v>
@@ -3213,16 +3213,16 @@
         </row>
         <row r="172">
           <cell r="AM172" t="str">
-            <v>超甲狂犀</v>
+            <v>帝牙盧卡</v>
           </cell>
           <cell r="AN172" t="str">
-            <v>岩石</v>
+            <v>龍</v>
           </cell>
           <cell r="AO172" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP172">
-            <v>202</v>
+            <v>225</v>
           </cell>
           <cell r="AQ172" t="str">
             <v>D</v>
@@ -3230,16 +3230,16 @@
         </row>
         <row r="173">
           <cell r="AM173" t="str">
-            <v>帝牙盧卡</v>
+            <v>帕路奇亞</v>
           </cell>
           <cell r="AN173" t="str">
-            <v>鋼</v>
+            <v>龍</v>
           </cell>
           <cell r="AO173" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP173">
-            <v>225</v>
+            <v>233</v>
           </cell>
           <cell r="AQ173" t="str">
             <v>D</v>
@@ -3247,16 +3247,16 @@
         </row>
         <row r="174">
           <cell r="AM174" t="str">
-            <v>帝牙盧卡</v>
+            <v>瑪狃拉</v>
           </cell>
           <cell r="AN174" t="str">
-            <v>龍</v>
+            <v>冰</v>
           </cell>
           <cell r="AO174" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP174">
-            <v>225</v>
+            <v>204</v>
           </cell>
           <cell r="AQ174" t="str">
             <v>D</v>
@@ -3264,64 +3264,70 @@
         </row>
         <row r="175">
           <cell r="AM175" t="str">
-            <v>帕路奇亞</v>
+            <v>超極巨鋁鋼龍</v>
           </cell>
           <cell r="AN175" t="str">
-            <v>龍</v>
+            <v>鋼</v>
           </cell>
           <cell r="AO175" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP175">
-            <v>233</v>
+            <v>201</v>
           </cell>
           <cell r="AQ175" t="str">
-            <v>D</v>
+            <v>G</v>
           </cell>
         </row>
         <row r="176">
           <cell r="AM176" t="str">
-            <v>超極巨鋁鋼龍</v>
+            <v>瑪狃拉</v>
           </cell>
           <cell r="AN176" t="str">
-            <v>鋼</v>
+            <v>惡</v>
           </cell>
           <cell r="AO176" t="str">
             <v>Y</v>
           </cell>
           <cell r="AP176">
-            <v>201</v>
+            <v>204</v>
           </cell>
           <cell r="AQ176" t="str">
-            <v>G</v>
+            <v>D</v>
           </cell>
         </row>
         <row r="177">
           <cell r="AM177" t="str">
-            <v/>
+            <v>焚焰蚣</v>
           </cell>
           <cell r="AN177" t="str">
-            <v/>
-          </cell>
-          <cell r="AP177" t="str">
-            <v/>
+            <v>火</v>
+          </cell>
+          <cell r="AO177" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP177">
+            <v>186</v>
           </cell>
           <cell r="AQ177" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="178">
           <cell r="AM178" t="str">
-            <v/>
+            <v>焚焰蚣</v>
           </cell>
           <cell r="AN178" t="str">
-            <v/>
-          </cell>
-          <cell r="AP178" t="str">
-            <v/>
+            <v>蟲</v>
+          </cell>
+          <cell r="AO178" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP178">
+            <v>186</v>
           </cell>
           <cell r="AQ178" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="179">
@@ -3330,6 +3336,9 @@
           </cell>
           <cell r="AN179" t="str">
             <v/>
+          </cell>
+          <cell r="AO179" t="str">
+            <v>Y</v>
           </cell>
           <cell r="AP179" t="str">
             <v/>
@@ -6033,7 +6042,7 @@
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="13" t="str">
         <f>IF([1]攻守數據!AM43 = "", "", [1]攻守數據!AM43)</f>
-        <v>閃電鳥</v>
+        <v>火焰鳥</v>
       </c>
       <c r="C42" s="13" t="str">
         <f>IF([1]攻守數據!AN43 = "", "", [1]攻守數據!AN43)</f>
@@ -6045,7 +6054,7 @@
       </c>
       <c r="E42" s="13">
         <f>IF([1]攻守數據!AP43 = "", "", [1]攻守數據!AP43)</f>
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F42" s="13" t="str">
         <f>IF([1]攻守數據!AQ43 = "", "", [1]攻守數據!AQ43)</f>
@@ -6059,7 +6068,7 @@
       </c>
       <c r="C43" s="13" t="str">
         <f>IF([1]攻守數據!AN44 = "", "", [1]攻守數據!AN44)</f>
-        <v>飛行</v>
+        <v>火</v>
       </c>
       <c r="D43" s="13" t="str">
         <f>IF([1]攻守數據!AO44 = "", "", [1]攻守數據!AO44)</f>
@@ -6077,11 +6086,11 @@
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="13" t="str">
         <f>IF([1]攻守數據!AM45 = "", "", [1]攻守數據!AM45)</f>
-        <v>火焰鳥</v>
+        <v>藏瑪然特</v>
       </c>
       <c r="C44" s="13" t="str">
         <f>IF([1]攻守數據!AN45 = "", "", [1]攻守數據!AN45)</f>
-        <v>火</v>
+        <v>鋼</v>
       </c>
       <c r="D44" s="13" t="str">
         <f>IF([1]攻守數據!AO45 = "", "", [1]攻守數據!AO45)</f>
@@ -6089,7 +6098,7 @@
       </c>
       <c r="E44" s="13">
         <f>IF([1]攻守數據!AP45 = "", "", [1]攻守數據!AP45)</f>
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F44" s="13" t="str">
         <f>IF([1]攻守數據!AQ45 = "", "", [1]攻守數據!AQ45)</f>
@@ -6099,11 +6108,11 @@
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="13" t="str">
         <f>IF([1]攻守數據!AM46 = "", "", [1]攻守數據!AM46)</f>
-        <v>藏瑪然特</v>
+        <v>炎帝</v>
       </c>
       <c r="C45" s="13" t="str">
         <f>IF([1]攻守數據!AN46 = "", "", [1]攻守數據!AN46)</f>
-        <v>鋼</v>
+        <v>火</v>
       </c>
       <c r="D45" s="13" t="str">
         <f>IF([1]攻守數據!AO46 = "", "", [1]攻守數據!AO46)</f>
@@ -6111,7 +6120,7 @@
       </c>
       <c r="E45" s="13">
         <f>IF([1]攻守數據!AP46 = "", "", [1]攻守數據!AP46)</f>
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="F45" s="13" t="str">
         <f>IF([1]攻守數據!AQ46 = "", "", [1]攻守數據!AQ46)</f>
@@ -6121,11 +6130,11 @@
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="13" t="str">
         <f>IF([1]攻守數據!AM47 = "", "", [1]攻守數據!AM47)</f>
-        <v>炎帝</v>
+        <v>布莉姆溫</v>
       </c>
       <c r="C46" s="13" t="str">
         <f>IF([1]攻守數據!AN47 = "", "", [1]攻守數據!AN47)</f>
-        <v>火</v>
+        <v>超能力</v>
       </c>
       <c r="D46" s="13" t="str">
         <f>IF([1]攻守數據!AO47 = "", "", [1]攻守數據!AO47)</f>
@@ -6147,7 +6156,7 @@
       </c>
       <c r="C47" s="13" t="str">
         <f>IF([1]攻守數據!AN48 = "", "", [1]攻守數據!AN48)</f>
-        <v>超能力</v>
+        <v>妖精</v>
       </c>
       <c r="D47" s="13" t="str">
         <f>IF([1]攻守數據!AO48 = "", "", [1]攻守數據!AO48)</f>
@@ -6165,19 +6174,19 @@
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="13" t="str">
         <f>IF([1]攻守數據!AM49 = "", "", [1]攻守數據!AM49)</f>
-        <v>布莉姆溫</v>
+        <v>吼鯨王</v>
       </c>
       <c r="C48" s="13" t="str">
         <f>IF([1]攻守數據!AN49 = "", "", [1]攻守數據!AN49)</f>
-        <v>妖精</v>
+        <v>岩石</v>
       </c>
       <c r="D48" s="13" t="str">
         <f>IF([1]攻守數據!AO49 = "", "", [1]攻守數據!AO49)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E48" s="13">
         <f>IF([1]攻守數據!AP49 = "", "", [1]攻守數據!AP49)</f>
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="F48" s="13" t="str">
         <f>IF([1]攻守數據!AQ49 = "", "", [1]攻守數據!AQ49)</f>
@@ -6187,19 +6196,19 @@
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="13" t="str">
         <f>IF([1]攻守數據!AM50 = "", "", [1]攻守數據!AM50)</f>
-        <v>吼鯨王</v>
+        <v>拉帝亞斯</v>
       </c>
       <c r="C49" s="13" t="str">
         <f>IF([1]攻守數據!AN50 = "", "", [1]攻守數據!AN50)</f>
-        <v>岩石</v>
+        <v>超能力</v>
       </c>
       <c r="D49" s="13" t="str">
         <f>IF([1]攻守數據!AO50 = "", "", [1]攻守數據!AO50)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E49" s="13">
         <f>IF([1]攻守數據!AP50 = "", "", [1]攻守數據!AP50)</f>
-        <v>147</v>
+        <v>190</v>
       </c>
       <c r="F49" s="13" t="str">
         <f>IF([1]攻守數據!AQ50 = "", "", [1]攻守數據!AQ50)</f>
@@ -6213,7 +6222,7 @@
       </c>
       <c r="C50" s="13" t="str">
         <f>IF([1]攻守數據!AN51 = "", "", [1]攻守數據!AN51)</f>
-        <v>超能力</v>
+        <v>龍</v>
       </c>
       <c r="D50" s="13" t="str">
         <f>IF([1]攻守數據!AO51 = "", "", [1]攻守數據!AO51)</f>
@@ -6231,11 +6240,11 @@
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="13" t="str">
         <f>IF([1]攻守數據!AM52 = "", "", [1]攻守數據!AM52)</f>
-        <v>拉帝亞斯</v>
+        <v>高傲雉雞</v>
       </c>
       <c r="C51" s="13" t="str">
         <f>IF([1]攻守數據!AN52 = "", "", [1]攻守數據!AN52)</f>
-        <v>龍</v>
+        <v>飛行</v>
       </c>
       <c r="D51" s="13" t="str">
         <f>IF([1]攻守數據!AO52 = "", "", [1]攻守數據!AO52)</f>
@@ -6243,7 +6252,7 @@
       </c>
       <c r="E51" s="13">
         <f>IF([1]攻守數據!AP52 = "", "", [1]攻守數據!AP52)</f>
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F51" s="13" t="str">
         <f>IF([1]攻守數據!AQ52 = "", "", [1]攻守數據!AQ52)</f>
@@ -6253,11 +6262,11 @@
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="13" t="str">
         <f>IF([1]攻守數據!AM53 = "", "", [1]攻守數據!AM53)</f>
-        <v>高傲雉雞</v>
+        <v>超極巨巴大蝶</v>
       </c>
       <c r="C52" s="13" t="str">
         <f>IF([1]攻守數據!AN53 = "", "", [1]攻守數據!AN53)</f>
-        <v>飛行</v>
+        <v>蟲</v>
       </c>
       <c r="D52" s="13" t="str">
         <f>IF([1]攻守數據!AO53 = "", "", [1]攻守數據!AO53)</f>
@@ -6265,17 +6274,17 @@
       </c>
       <c r="E52" s="13">
         <f>IF([1]攻守數據!AP53 = "", "", [1]攻守數據!AP53)</f>
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="F52" s="13" t="str">
         <f>IF([1]攻守數據!AQ53 = "", "", [1]攻守數據!AQ53)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="13" t="str">
         <f>IF([1]攻守數據!AM54 = "", "", [1]攻守數據!AM54)</f>
-        <v>超極巨巴大蝶</v>
+        <v>巴大蝶</v>
       </c>
       <c r="C53" s="13" t="str">
         <f>IF([1]攻守數據!AN54 = "", "", [1]攻守數據!AN54)</f>
@@ -6291,7 +6300,7 @@
       </c>
       <c r="F53" s="13" t="str">
         <f>IF([1]攻守數據!AQ54 = "", "", [1]攻守數據!AQ54)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
@@ -6301,11 +6310,11 @@
       </c>
       <c r="C54" s="13" t="str">
         <f>IF([1]攻守數據!AN55 = "", "", [1]攻守數據!AN55)</f>
-        <v>蟲</v>
+        <v>超能力</v>
       </c>
       <c r="D54" s="13" t="str">
         <f>IF([1]攻守數據!AO55 = "", "", [1]攻守數據!AO55)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E54" s="13">
         <f>IF([1]攻守數據!AP55 = "", "", [1]攻守數據!AP55)</f>
@@ -6319,11 +6328,11 @@
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="13" t="str">
         <f>IF([1]攻守數據!AM56 = "", "", [1]攻守數據!AM56)</f>
-        <v>巴大蝶</v>
+        <v>藏飽栗鼠</v>
       </c>
       <c r="C55" s="13" t="str">
         <f>IF([1]攻守數據!AN56 = "", "", [1]攻守數據!AN56)</f>
-        <v>超能力</v>
+        <v>草</v>
       </c>
       <c r="D55" s="13" t="str">
         <f>IF([1]攻守數據!AO56 = "", "", [1]攻守數據!AO56)</f>
@@ -6331,7 +6340,7 @@
       </c>
       <c r="E55" s="13">
         <f>IF([1]攻守數據!AP56 = "", "", [1]攻守數據!AP56)</f>
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F55" s="13" t="str">
         <f>IF([1]攻守數據!AQ56 = "", "", [1]攻守數據!AQ56)</f>
@@ -6341,11 +6350,11 @@
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="13" t="str">
         <f>IF([1]攻守數據!AM57 = "", "", [1]攻守數據!AM57)</f>
-        <v>藏飽栗鼠</v>
+        <v>毛毛角羊</v>
       </c>
       <c r="C56" s="13" t="str">
         <f>IF([1]攻守數據!AN57 = "", "", [1]攻守數據!AN57)</f>
-        <v>草</v>
+        <v>格鬥</v>
       </c>
       <c r="D56" s="13" t="str">
         <f>IF([1]攻守數據!AO57 = "", "", [1]攻守數據!AO57)</f>
@@ -6353,7 +6362,7 @@
       </c>
       <c r="E56" s="13">
         <f>IF([1]攻守數據!AP57 = "", "", [1]攻守數據!AP57)</f>
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F56" s="13" t="str">
         <f>IF([1]攻守數據!AQ57 = "", "", [1]攻守數據!AQ57)</f>
@@ -6363,29 +6372,29 @@
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="13" t="str">
         <f>IF([1]攻守數據!AM58 = "", "", [1]攻守數據!AM58)</f>
-        <v>毛毛角羊</v>
+        <v>超極巨千面避役</v>
       </c>
       <c r="C57" s="13" t="str">
         <f>IF([1]攻守數據!AN58 = "", "", [1]攻守數據!AN58)</f>
-        <v>格鬥</v>
+        <v>水</v>
       </c>
       <c r="D57" s="13" t="str">
         <f>IF([1]攻守數據!AO58 = "", "", [1]攻守數據!AO58)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E57" s="13">
         <f>IF([1]攻守數據!AP58 = "", "", [1]攻守數據!AP58)</f>
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="F57" s="13" t="str">
         <f>IF([1]攻守數據!AQ58 = "", "", [1]攻守數據!AQ58)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="13" t="str">
         <f>IF([1]攻守數據!AM59 = "", "", [1]攻守數據!AM59)</f>
-        <v>超極巨千面避役</v>
+        <v>千面避役</v>
       </c>
       <c r="C58" s="13" t="str">
         <f>IF([1]攻守數據!AN59 = "", "", [1]攻守數據!AN59)</f>
@@ -6401,13 +6410,13 @@
       </c>
       <c r="F58" s="13" t="str">
         <f>IF([1]攻守數據!AQ59 = "", "", [1]攻守數據!AQ59)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="13" t="str">
         <f>IF([1]攻守數據!AM60 = "", "", [1]攻守數據!AM60)</f>
-        <v>千面避役</v>
+        <v>超極巨巨鉗蟹</v>
       </c>
       <c r="C59" s="13" t="str">
         <f>IF([1]攻守數據!AN60 = "", "", [1]攻守數據!AN60)</f>
@@ -6419,25 +6428,25 @@
       </c>
       <c r="E59" s="13">
         <f>IF([1]攻守數據!AP60 = "", "", [1]攻守數據!AP60)</f>
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="F59" s="13" t="str">
         <f>IF([1]攻守數據!AQ60 = "", "", [1]攻守數據!AQ60)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="13" t="str">
         <f>IF([1]攻守數據!AM61 = "", "", [1]攻守數據!AM61)</f>
-        <v>超極巨巨鉗蟹</v>
+        <v>巨鉗蟹</v>
       </c>
       <c r="C60" s="13" t="str">
         <f>IF([1]攻守數據!AN61 = "", "", [1]攻守數據!AN61)</f>
-        <v>水</v>
+        <v>地面</v>
       </c>
       <c r="D60" s="13" t="str">
         <f>IF([1]攻守數據!AO61 = "", "", [1]攻守數據!AO61)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E60" s="13">
         <f>IF([1]攻守數據!AP61 = "", "", [1]攻守數據!AP61)</f>
@@ -6445,7 +6454,7 @@
       </c>
       <c r="F60" s="13" t="str">
         <f>IF([1]攻守數據!AQ61 = "", "", [1]攻守數據!AQ61)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
@@ -6455,7 +6464,7 @@
       </c>
       <c r="C61" s="13" t="str">
         <f>IF([1]攻守數據!AN62 = "", "", [1]攻守數據!AN62)</f>
-        <v>地面</v>
+        <v>鋼</v>
       </c>
       <c r="D61" s="13" t="str">
         <f>IF([1]攻守數據!AO62 = "", "", [1]攻守數據!AO62)</f>
@@ -6473,7 +6482,7 @@
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62" s="13" t="str">
         <f>IF([1]攻守數據!AM63 = "", "", [1]攻守數據!AM63)</f>
-        <v>巨鉗蟹</v>
+        <v>高傲雉雞</v>
       </c>
       <c r="C62" s="13" t="str">
         <f>IF([1]攻守數據!AN63 = "", "", [1]攻守數據!AN63)</f>
@@ -6485,7 +6494,7 @@
       </c>
       <c r="E62" s="13">
         <f>IF([1]攻守數據!AP63 = "", "", [1]攻守數據!AP63)</f>
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="F62" s="13" t="str">
         <f>IF([1]攻守數據!AQ63 = "", "", [1]攻守數據!AQ63)</f>
@@ -6495,11 +6504,11 @@
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="13" t="str">
         <f>IF([1]攻守數據!AM64 = "", "", [1]攻守數據!AM64)</f>
-        <v>高傲雉雞</v>
+        <v>鐮刀盔</v>
       </c>
       <c r="C63" s="13" t="str">
         <f>IF([1]攻守數據!AN64 = "", "", [1]攻守數據!AN64)</f>
-        <v>鋼</v>
+        <v>地面</v>
       </c>
       <c r="D63" s="13" t="str">
         <f>IF([1]攻守數據!AO64 = "", "", [1]攻守數據!AO64)</f>
@@ -6507,7 +6516,7 @@
       </c>
       <c r="E63" s="13">
         <f>IF([1]攻守數據!AP64 = "", "", [1]攻守數據!AP64)</f>
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F63" s="13" t="str">
         <f>IF([1]攻守數據!AQ64 = "", "", [1]攻守數據!AQ64)</f>
@@ -6521,7 +6530,7 @@
       </c>
       <c r="C64" s="13" t="str">
         <f>IF([1]攻守數據!AN65 = "", "", [1]攻守數據!AN65)</f>
-        <v>地面</v>
+        <v>蟲</v>
       </c>
       <c r="D64" s="13" t="str">
         <f>IF([1]攻守數據!AO65 = "", "", [1]攻守數據!AO65)</f>
@@ -6539,11 +6548,11 @@
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B65" s="13" t="str">
         <f>IF([1]攻守數據!AM66 = "", "", [1]攻守數據!AM66)</f>
-        <v>鐮刀盔</v>
+        <v>多刺菊石獸</v>
       </c>
       <c r="C65" s="13" t="str">
         <f>IF([1]攻守數據!AN66 = "", "", [1]攻守數據!AN66)</f>
-        <v>蟲</v>
+        <v>地面</v>
       </c>
       <c r="D65" s="13" t="str">
         <f>IF([1]攻守數據!AO66 = "", "", [1]攻守數據!AO66)</f>
@@ -6551,7 +6560,7 @@
       </c>
       <c r="E65" s="13">
         <f>IF([1]攻守數據!AP66 = "", "", [1]攻守數據!AP66)</f>
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F65" s="13" t="str">
         <f>IF([1]攻守數據!AQ66 = "", "", [1]攻守數據!AQ66)</f>
@@ -6561,19 +6570,19 @@
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B66" s="13" t="str">
         <f>IF([1]攻守數據!AM67 = "", "", [1]攻守數據!AM67)</f>
-        <v>多刺菊石獸</v>
+        <v>巴大蝶</v>
       </c>
       <c r="C66" s="13" t="str">
         <f>IF([1]攻守數據!AN67 = "", "", [1]攻守數據!AN67)</f>
-        <v>地面</v>
+        <v>蟲</v>
       </c>
       <c r="D66" s="13" t="str">
         <f>IF([1]攻守數據!AO67 = "", "", [1]攻守數據!AO67)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E66" s="13">
         <f>IF([1]攻守數據!AP67 = "", "", [1]攻守數據!AP67)</f>
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="F66" s="13" t="str">
         <f>IF([1]攻守數據!AQ67 = "", "", [1]攻守數據!AQ67)</f>
@@ -6583,11 +6592,11 @@
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B67" s="13" t="str">
         <f>IF([1]攻守數據!AM68 = "", "", [1]攻守數據!AM68)</f>
-        <v>巴大蝶</v>
+        <v>鋼鎧鴉</v>
       </c>
       <c r="C67" s="13" t="str">
         <f>IF([1]攻守數據!AN68 = "", "", [1]攻守數據!AN68)</f>
-        <v>蟲</v>
+        <v>飛行</v>
       </c>
       <c r="D67" s="13" t="str">
         <f>IF([1]攻守數據!AO68 = "", "", [1]攻守數據!AO68)</f>
@@ -6595,7 +6604,7 @@
       </c>
       <c r="E67" s="13">
         <f>IF([1]攻守數據!AP68 = "", "", [1]攻守數據!AP68)</f>
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F67" s="13" t="str">
         <f>IF([1]攻守數據!AQ68 = "", "", [1]攻守數據!AQ68)</f>
@@ -6609,7 +6618,7 @@
       </c>
       <c r="C68" s="13" t="str">
         <f>IF([1]攻守數據!AN69 = "", "", [1]攻守數據!AN69)</f>
-        <v>飛行</v>
+        <v>鋼</v>
       </c>
       <c r="D68" s="13" t="str">
         <f>IF([1]攻守數據!AO69 = "", "", [1]攻守數據!AO69)</f>
@@ -6631,11 +6640,11 @@
       </c>
       <c r="C69" s="13" t="str">
         <f>IF([1]攻守數據!AN70 = "", "", [1]攻守數據!AN70)</f>
-        <v>鋼</v>
+        <v>地面</v>
       </c>
       <c r="D69" s="13" t="str">
         <f>IF([1]攻守數據!AO70 = "", "", [1]攻守數據!AO70)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E69" s="13">
         <f>IF([1]攻守數據!AP70 = "", "", [1]攻守數據!AP70)</f>
@@ -6649,37 +6658,37 @@
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B70" s="13" t="str">
         <f>IF([1]攻守數據!AM71 = "", "", [1]攻守數據!AM71)</f>
-        <v>鋼鎧鴉</v>
+        <v>超極巨灰塵山</v>
       </c>
       <c r="C70" s="13" t="str">
         <f>IF([1]攻守數據!AN71 = "", "", [1]攻守數據!AN71)</f>
-        <v>地面</v>
+        <v>毒</v>
       </c>
       <c r="D70" s="13" t="str">
         <f>IF([1]攻守數據!AO71 = "", "", [1]攻守數據!AO71)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E70" s="13">
         <f>IF([1]攻守數據!AP71 = "", "", [1]攻守數據!AP71)</f>
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="F70" s="13" t="str">
         <f>IF([1]攻守數據!AQ71 = "", "", [1]攻守數據!AQ71)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B71" s="13" t="str">
         <f>IF([1]攻守數據!AM72 = "", "", [1]攻守數據!AM72)</f>
-        <v>超極巨灰塵山</v>
+        <v>灰塵山</v>
       </c>
       <c r="C71" s="13" t="str">
         <f>IF([1]攻守數據!AN72 = "", "", [1]攻守數據!AN72)</f>
-        <v>毒</v>
+        <v>蟲</v>
       </c>
       <c r="D71" s="13" t="str">
         <f>IF([1]攻守數據!AO72 = "", "", [1]攻守數據!AO72)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E71" s="13">
         <f>IF([1]攻守數據!AP72 = "", "", [1]攻守數據!AP72)</f>
@@ -6687,17 +6696,17 @@
       </c>
       <c r="F71" s="13" t="str">
         <f>IF([1]攻守數據!AQ72 = "", "", [1]攻守數據!AQ72)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B72" s="13" t="str">
         <f>IF([1]攻守數據!AM73 = "", "", [1]攻守數據!AM73)</f>
-        <v>灰塵山</v>
+        <v>吼鯨王</v>
       </c>
       <c r="C72" s="13" t="str">
         <f>IF([1]攻守數據!AN73 = "", "", [1]攻守數據!AN73)</f>
-        <v>蟲</v>
+        <v>超能力</v>
       </c>
       <c r="D72" s="13" t="str">
         <f>IF([1]攻守數據!AO73 = "", "", [1]攻守數據!AO73)</f>
@@ -6705,7 +6714,7 @@
       </c>
       <c r="E72" s="13">
         <f>IF([1]攻守數據!AP73 = "", "", [1]攻守數據!AP73)</f>
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F72" s="13" t="str">
         <f>IF([1]攻守數據!AQ73 = "", "", [1]攻守數據!AQ73)</f>
@@ -6715,29 +6724,29 @@
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B73" s="13" t="str">
         <f>IF([1]攻守數據!AM74 = "", "", [1]攻守數據!AM74)</f>
-        <v>吼鯨王</v>
+        <v>超極巨水箭龜</v>
       </c>
       <c r="C73" s="13" t="str">
         <f>IF([1]攻守數據!AN74 = "", "", [1]攻守數據!AN74)</f>
-        <v>超能力</v>
+        <v>水</v>
       </c>
       <c r="D73" s="13" t="str">
         <f>IF([1]攻守數據!AO74 = "", "", [1]攻守數據!AO74)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E73" s="13">
         <f>IF([1]攻守數據!AP74 = "", "", [1]攻守數據!AP74)</f>
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F73" s="13" t="str">
         <f>IF([1]攻守數據!AQ74 = "", "", [1]攻守數據!AQ74)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B74" s="13" t="str">
         <f>IF([1]攻守數據!AM75 = "", "", [1]攻守數據!AM75)</f>
-        <v>超極巨水箭龜</v>
+        <v>水箭龜</v>
       </c>
       <c r="C74" s="13" t="str">
         <f>IF([1]攻守數據!AN75 = "", "", [1]攻守數據!AN75)</f>
@@ -6753,7 +6762,7 @@
       </c>
       <c r="F74" s="13" t="str">
         <f>IF([1]攻守數據!AQ75 = "", "", [1]攻守數據!AQ75)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.3">
@@ -6763,11 +6772,11 @@
       </c>
       <c r="C75" s="13" t="str">
         <f>IF([1]攻守數據!AN76 = "", "", [1]攻守數據!AN76)</f>
-        <v>水</v>
+        <v>岩石</v>
       </c>
       <c r="D75" s="13" t="str">
         <f>IF([1]攻守數據!AO76 = "", "", [1]攻守數據!AO76)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E75" s="13">
         <f>IF([1]攻守數據!AP76 = "", "", [1]攻守數據!AP76)</f>
@@ -6785,7 +6794,7 @@
       </c>
       <c r="C76" s="13" t="str">
         <f>IF([1]攻守數據!AN77 = "", "", [1]攻守數據!AN77)</f>
-        <v>岩石</v>
+        <v>惡</v>
       </c>
       <c r="D76" s="13" t="str">
         <f>IF([1]攻守數據!AO77 = "", "", [1]攻守數據!AO77)</f>
@@ -6803,19 +6812,19 @@
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B77" s="13" t="str">
         <f>IF([1]攻守數據!AM78 = "", "", [1]攻守數據!AM78)</f>
-        <v>水箭龜</v>
+        <v>勾魂眼</v>
       </c>
       <c r="C77" s="13" t="str">
         <f>IF([1]攻守數據!AN78 = "", "", [1]攻守數據!AN78)</f>
-        <v>惡</v>
+        <v>幽靈</v>
       </c>
       <c r="D77" s="13" t="str">
         <f>IF([1]攻守數據!AO78 = "", "", [1]攻守數據!AO78)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E77" s="13">
         <f>IF([1]攻守數據!AP78 = "", "", [1]攻守數據!AP78)</f>
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="F77" s="13" t="str">
         <f>IF([1]攻守數據!AQ78 = "", "", [1]攻守數據!AQ78)</f>
@@ -6829,7 +6838,7 @@
       </c>
       <c r="C78" s="13" t="str">
         <f>IF([1]攻守數據!AN79 = "", "", [1]攻守數據!AN79)</f>
-        <v>幽靈</v>
+        <v>惡</v>
       </c>
       <c r="D78" s="13" t="str">
         <f>IF([1]攻守數據!AO79 = "", "", [1]攻守數據!AO79)</f>
@@ -6847,11 +6856,11 @@
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="13" t="str">
         <f>IF([1]攻守數據!AM80 = "", "", [1]攻守數據!AM80)</f>
-        <v>勾魂眼</v>
+        <v>鐮刀盔</v>
       </c>
       <c r="C79" s="13" t="str">
         <f>IF([1]攻守數據!AN80 = "", "", [1]攻守數據!AN80)</f>
-        <v>惡</v>
+        <v>水</v>
       </c>
       <c r="D79" s="13" t="str">
         <f>IF([1]攻守數據!AO80 = "", "", [1]攻守數據!AO80)</f>
@@ -6859,7 +6868,7 @@
       </c>
       <c r="E79" s="13">
         <f>IF([1]攻守數據!AP80 = "", "", [1]攻守數據!AP80)</f>
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="F79" s="13" t="str">
         <f>IF([1]攻守數據!AQ80 = "", "", [1]攻守數據!AQ80)</f>
@@ -6869,19 +6878,19 @@
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" s="13" t="str">
         <f>IF([1]攻守數據!AM81 = "", "", [1]攻守數據!AM81)</f>
-        <v>鐮刀盔</v>
+        <v>藏飽栗鼠</v>
       </c>
       <c r="C80" s="13" t="str">
         <f>IF([1]攻守數據!AN81 = "", "", [1]攻守數據!AN81)</f>
-        <v>水</v>
+        <v>地面</v>
       </c>
       <c r="D80" s="13" t="str">
         <f>IF([1]攻守數據!AO81 = "", "", [1]攻守數據!AO81)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E80" s="13">
         <f>IF([1]攻守數據!AP81 = "", "", [1]攻守數據!AP81)</f>
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="F80" s="13" t="str">
         <f>IF([1]攻守數據!AQ81 = "", "", [1]攻守數據!AQ81)</f>
@@ -6895,7 +6904,7 @@
       </c>
       <c r="C81" s="13" t="str">
         <f>IF([1]攻守數據!AN82 = "", "", [1]攻守數據!AN82)</f>
-        <v>地面</v>
+        <v>惡</v>
       </c>
       <c r="D81" s="13" t="str">
         <f>IF([1]攻守數據!AO82 = "", "", [1]攻守數據!AO82)</f>
@@ -6913,19 +6922,19 @@
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" s="13" t="str">
         <f>IF([1]攻守數據!AM83 = "", "", [1]攻守數據!AM83)</f>
-        <v>藏飽栗鼠</v>
+        <v>多刺菊石獸</v>
       </c>
       <c r="C82" s="13" t="str">
         <f>IF([1]攻守數據!AN83 = "", "", [1]攻守數據!AN83)</f>
-        <v>惡</v>
+        <v>水</v>
       </c>
       <c r="D82" s="13" t="str">
         <f>IF([1]攻守數據!AO83 = "", "", [1]攻守數據!AO83)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E82" s="13">
         <f>IF([1]攻守數據!AP83 = "", "", [1]攻守數據!AP83)</f>
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="F82" s="13" t="str">
         <f>IF([1]攻守數據!AQ83 = "", "", [1]攻守數據!AQ83)</f>
@@ -6935,7 +6944,7 @@
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B83" s="13" t="str">
         <f>IF([1]攻守數據!AM84 = "", "", [1]攻守數據!AM84)</f>
-        <v>多刺菊石獸</v>
+        <v>水君</v>
       </c>
       <c r="C83" s="13" t="str">
         <f>IF([1]攻守數據!AN84 = "", "", [1]攻守數據!AN84)</f>
@@ -6947,7 +6956,7 @@
       </c>
       <c r="E83" s="13">
         <f>IF([1]攻守數據!AP84 = "", "", [1]攻守數據!AP84)</f>
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="F83" s="13" t="str">
         <f>IF([1]攻守數據!AQ84 = "", "", [1]攻守數據!AQ84)</f>
@@ -6957,7 +6966,7 @@
     <row r="84" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B84" s="13" t="str">
         <f>IF([1]攻守數據!AM85 = "", "", [1]攻守數據!AM85)</f>
-        <v>水君</v>
+        <v>吼鯨王</v>
       </c>
       <c r="C84" s="13" t="str">
         <f>IF([1]攻守數據!AN85 = "", "", [1]攻守數據!AN85)</f>
@@ -6969,7 +6978,7 @@
       </c>
       <c r="E84" s="13">
         <f>IF([1]攻守數據!AP85 = "", "", [1]攻守數據!AP85)</f>
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F84" s="13" t="str">
         <f>IF([1]攻守數據!AQ85 = "", "", [1]攻守數據!AQ85)</f>
@@ -6979,19 +6988,19 @@
     <row r="85" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B85" s="13" t="str">
         <f>IF([1]攻守數據!AM86 = "", "", [1]攻守數據!AM86)</f>
-        <v>吼鯨王</v>
+        <v>幸福蛋</v>
       </c>
       <c r="C85" s="13" t="str">
         <f>IF([1]攻守數據!AN86 = "", "", [1]攻守數據!AN86)</f>
-        <v>水</v>
+        <v>超能力</v>
       </c>
       <c r="D85" s="13" t="str">
         <f>IF([1]攻守數據!AO86 = "", "", [1]攻守數據!AO86)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E85" s="13">
         <f>IF([1]攻守數據!AP86 = "", "", [1]攻守數據!AP86)</f>
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="F85" s="13" t="str">
         <f>IF([1]攻守數據!AQ86 = "", "", [1]攻守數據!AQ86)</f>
@@ -7001,19 +7010,19 @@
     <row r="86" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B86" s="13" t="str">
         <f>IF([1]攻守數據!AM87 = "", "", [1]攻守數據!AM87)</f>
-        <v>幸福蛋</v>
+        <v>急凍鳥</v>
       </c>
       <c r="C86" s="13" t="str">
         <f>IF([1]攻守數據!AN87 = "", "", [1]攻守數據!AN87)</f>
-        <v>超能力</v>
+        <v>冰</v>
       </c>
       <c r="D86" s="13" t="str">
         <f>IF([1]攻守數據!AO87 = "", "", [1]攻守數據!AO87)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E86" s="13">
         <f>IF([1]攻守數據!AP87 = "", "", [1]攻守數據!AP87)</f>
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="F86" s="13" t="str">
         <f>IF([1]攻守數據!AQ87 = "", "", [1]攻守數據!AQ87)</f>
@@ -7023,7 +7032,7 @@
     <row r="87" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B87" s="13" t="str">
         <f>IF([1]攻守數據!AM88 = "", "", [1]攻守數據!AM88)</f>
-        <v>急凍鳥</v>
+        <v>幾何雪花</v>
       </c>
       <c r="C87" s="13" t="str">
         <f>IF([1]攻守數據!AN88 = "", "", [1]攻守數據!AN88)</f>
@@ -7035,7 +7044,7 @@
       </c>
       <c r="E87" s="13">
         <f>IF([1]攻守數據!AP88 = "", "", [1]攻守數據!AP88)</f>
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F87" s="13" t="str">
         <f>IF([1]攻守數據!AQ88 = "", "", [1]攻守數據!AQ88)</f>
@@ -7045,11 +7054,11 @@
     <row r="88" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B88" s="13" t="str">
         <f>IF([1]攻守數據!AM89 = "", "", [1]攻守數據!AM89)</f>
-        <v>幾何雪花</v>
+        <v>壺壺</v>
       </c>
       <c r="C88" s="13" t="str">
         <f>IF([1]攻守數據!AN89 = "", "", [1]攻守數據!AN89)</f>
-        <v>冰</v>
+        <v>岩石</v>
       </c>
       <c r="D88" s="13" t="str">
         <f>IF([1]攻守數據!AO89 = "", "", [1]攻守數據!AO89)</f>
@@ -7057,7 +7066,7 @@
       </c>
       <c r="E88" s="13">
         <f>IF([1]攻守數據!AP89 = "", "", [1]攻守數據!AP89)</f>
-        <v>162</v>
+        <v>17</v>
       </c>
       <c r="F88" s="13" t="str">
         <f>IF([1]攻守數據!AQ89 = "", "", [1]攻守數據!AQ89)</f>
@@ -7071,7 +7080,7 @@
       </c>
       <c r="C89" s="13" t="str">
         <f>IF([1]攻守數據!AN90 = "", "", [1]攻守數據!AN90)</f>
-        <v>岩石</v>
+        <v>蟲</v>
       </c>
       <c r="D89" s="13" t="str">
         <f>IF([1]攻守數據!AO90 = "", "", [1]攻守數據!AO90)</f>
@@ -7089,11 +7098,11 @@
     <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B90" s="13" t="str">
         <f>IF([1]攻守數據!AM91 = "", "", [1]攻守數據!AM91)</f>
-        <v>壺壺</v>
+        <v>胡地</v>
       </c>
       <c r="C90" s="13" t="str">
         <f>IF([1]攻守數據!AN91 = "", "", [1]攻守數據!AN91)</f>
-        <v>蟲</v>
+        <v>超能力</v>
       </c>
       <c r="D90" s="13" t="str">
         <f>IF([1]攻守數據!AO91 = "", "", [1]攻守數據!AO91)</f>
@@ -7101,7 +7110,7 @@
       </c>
       <c r="E90" s="13">
         <f>IF([1]攻守數據!AP91 = "", "", [1]攻守數據!AP91)</f>
-        <v>17</v>
+        <v>225</v>
       </c>
       <c r="F90" s="13" t="str">
         <f>IF([1]攻守數據!AQ91 = "", "", [1]攻守數據!AQ91)</f>
@@ -7115,11 +7124,11 @@
       </c>
       <c r="C91" s="13" t="str">
         <f>IF([1]攻守數據!AN92 = "", "", [1]攻守數據!AN92)</f>
-        <v>超能力</v>
+        <v>格鬥</v>
       </c>
       <c r="D91" s="13" t="str">
         <f>IF([1]攻守數據!AO92 = "", "", [1]攻守數據!AO92)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E91" s="13">
         <f>IF([1]攻守數據!AP92 = "", "", [1]攻守數據!AP92)</f>
@@ -7133,33 +7142,33 @@
     <row r="92" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B92" s="13" t="str">
         <f>IF([1]攻守數據!AM93 = "", "", [1]攻守數據!AM93)</f>
-        <v>胡地</v>
+        <v>超極巨拉普拉斯</v>
       </c>
       <c r="C92" s="13" t="str">
         <f>IF([1]攻守數據!AN93 = "", "", [1]攻守數據!AN93)</f>
-        <v>格鬥</v>
+        <v>冰</v>
       </c>
       <c r="D92" s="13" t="str">
         <f>IF([1]攻守數據!AO93 = "", "", [1]攻守數據!AO93)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E92" s="13">
         <f>IF([1]攻守數據!AP93 = "", "", [1]攻守數據!AP93)</f>
-        <v>225</v>
+        <v>141</v>
       </c>
       <c r="F92" s="13" t="str">
         <f>IF([1]攻守數據!AQ93 = "", "", [1]攻守數據!AQ93)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B93" s="13" t="str">
         <f>IF([1]攻守數據!AM94 = "", "", [1]攻守數據!AM94)</f>
-        <v>超極巨拉普拉斯</v>
+        <v>鋁鋼龍</v>
       </c>
       <c r="C93" s="13" t="str">
         <f>IF([1]攻守數據!AN94 = "", "", [1]攻守數據!AN94)</f>
-        <v>冰</v>
+        <v>鋼</v>
       </c>
       <c r="D93" s="13" t="str">
         <f>IF([1]攻守數據!AO94 = "", "", [1]攻守數據!AO94)</f>
@@ -7167,11 +7176,11 @@
       </c>
       <c r="E93" s="13">
         <f>IF([1]攻守數據!AP94 = "", "", [1]攻守數據!AP94)</f>
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="F93" s="13" t="str">
         <f>IF([1]攻守數據!AQ94 = "", "", [1]攻守數據!AQ94)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.3">
@@ -7181,7 +7190,7 @@
       </c>
       <c r="C94" s="13" t="str">
         <f>IF([1]攻守數據!AN95 = "", "", [1]攻守數據!AN95)</f>
-        <v>鋼</v>
+        <v>龍</v>
       </c>
       <c r="D94" s="13" t="str">
         <f>IF([1]攻守數據!AO95 = "", "", [1]攻守數據!AO95)</f>
@@ -7203,11 +7212,11 @@
       </c>
       <c r="C95" s="13" t="str">
         <f>IF([1]攻守數據!AN96 = "", "", [1]攻守數據!AN96)</f>
-        <v>龍</v>
+        <v>一般</v>
       </c>
       <c r="D95" s="13" t="str">
         <f>IF([1]攻守數據!AO96 = "", "", [1]攻守數據!AO96)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E95" s="13">
         <f>IF([1]攻守數據!AP96 = "", "", [1]攻守數據!AP96)</f>
@@ -7221,11 +7230,11 @@
     <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B96" s="13" t="str">
         <f>IF([1]攻守數據!AM97 = "", "", [1]攻守數據!AM97)</f>
-        <v>鋁鋼龍</v>
+        <v>巨金怪</v>
       </c>
       <c r="C96" s="13" t="str">
         <f>IF([1]攻守數據!AN97 = "", "", [1]攻守數據!AN97)</f>
-        <v>一般</v>
+        <v>幽靈</v>
       </c>
       <c r="D96" s="13" t="str">
         <f>IF([1]攻守數據!AO97 = "", "", [1]攻守數據!AO97)</f>
@@ -7233,7 +7242,7 @@
       </c>
       <c r="E96" s="13">
         <f>IF([1]攻守數據!AP97 = "", "", [1]攻守數據!AP97)</f>
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="F96" s="13" t="str">
         <f>IF([1]攻守數據!AQ97 = "", "", [1]攻守數據!AQ97)</f>
@@ -7243,19 +7252,19 @@
     <row r="97" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B97" s="13" t="str">
         <f>IF([1]攻守數據!AM98 = "", "", [1]攻守數據!AM98)</f>
-        <v>巨金怪</v>
+        <v>沙奈朵</v>
       </c>
       <c r="C97" s="13" t="str">
         <f>IF([1]攻守數據!AN98 = "", "", [1]攻守數據!AN98)</f>
-        <v>幽靈</v>
+        <v>妖精</v>
       </c>
       <c r="D97" s="13" t="str">
         <f>IF([1]攻守數據!AO98 = "", "", [1]攻守數據!AO98)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E97" s="13">
         <f>IF([1]攻守數據!AP98 = "", "", [1]攻守數據!AP98)</f>
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="F97" s="13" t="str">
         <f>IF([1]攻守數據!AQ98 = "", "", [1]攻守數據!AQ98)</f>
@@ -7269,7 +7278,7 @@
       </c>
       <c r="C98" s="13" t="str">
         <f>IF([1]攻守數據!AN99 = "", "", [1]攻守數據!AN99)</f>
-        <v>妖精</v>
+        <v>超能力</v>
       </c>
       <c r="D98" s="13" t="str">
         <f>IF([1]攻守數據!AO99 = "", "", [1]攻守數據!AO99)</f>
@@ -7291,11 +7300,11 @@
       </c>
       <c r="C99" s="13" t="str">
         <f>IF([1]攻守數據!AN100 = "", "", [1]攻守數據!AN100)</f>
-        <v>超能力</v>
+        <v>草</v>
       </c>
       <c r="D99" s="13" t="str">
         <f>IF([1]攻守數據!AO100 = "", "", [1]攻守數據!AO100)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E99" s="13">
         <f>IF([1]攻守數據!AP100 = "", "", [1]攻守數據!AP100)</f>
@@ -7313,7 +7322,7 @@
       </c>
       <c r="C100" s="13" t="str">
         <f>IF([1]攻守數據!AN101 = "", "", [1]攻守數據!AN101)</f>
-        <v>草</v>
+        <v>電</v>
       </c>
       <c r="D100" s="13" t="str">
         <f>IF([1]攻守數據!AO101 = "", "", [1]攻守數據!AO101)</f>
@@ -7331,19 +7340,19 @@
     <row r="101" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B101" s="13" t="str">
         <f>IF([1]攻守數據!AM102 = "", "", [1]攻守數據!AM102)</f>
-        <v>沙奈朵</v>
+        <v>甜冷美后</v>
       </c>
       <c r="C101" s="13" t="str">
         <f>IF([1]攻守數據!AN102 = "", "", [1]攻守數據!AN102)</f>
-        <v>電</v>
+        <v>草</v>
       </c>
       <c r="D101" s="13" t="str">
         <f>IF([1]攻守數據!AO102 = "", "", [1]攻守數據!AO102)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E101" s="13">
         <f>IF([1]攻守數據!AP102 = "", "", [1]攻守數據!AP102)</f>
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F101" s="13" t="str">
         <f>IF([1]攻守數據!AQ102 = "", "", [1]攻守數據!AQ102)</f>
@@ -7357,11 +7366,11 @@
       </c>
       <c r="C102" s="13" t="str">
         <f>IF([1]攻守數據!AN103 = "", "", [1]攻守數據!AN103)</f>
-        <v>草</v>
+        <v>妖精</v>
       </c>
       <c r="D102" s="13" t="str">
         <f>IF([1]攻守數據!AO103 = "", "", [1]攻守數據!AO103)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E102" s="13">
         <f>IF([1]攻守數據!AP103 = "", "", [1]攻守數據!AP103)</f>
@@ -7375,33 +7384,33 @@
     <row r="103" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B103" s="13" t="str">
         <f>IF([1]攻守數據!AM104 = "", "", [1]攻守數據!AM104)</f>
-        <v>甜冷美后</v>
+        <v>超極巨伊布</v>
       </c>
       <c r="C103" s="13" t="str">
         <f>IF([1]攻守數據!AN104 = "", "", [1]攻守數據!AN104)</f>
-        <v>妖精</v>
+        <v>一般</v>
       </c>
       <c r="D103" s="13" t="str">
         <f>IF([1]攻守數據!AO104 = "", "", [1]攻守數據!AO104)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E103" s="13">
         <f>IF([1]攻守數據!AP104 = "", "", [1]攻守數據!AP104)</f>
-        <v>187</v>
+        <v>94</v>
       </c>
       <c r="F103" s="13" t="str">
         <f>IF([1]攻守數據!AQ104 = "", "", [1]攻守數據!AQ104)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B104" s="13" t="str">
         <f>IF([1]攻守數據!AM105 = "", "", [1]攻守數據!AM105)</f>
-        <v>超極巨伊布</v>
+        <v>水伊布</v>
       </c>
       <c r="C104" s="13" t="str">
         <f>IF([1]攻守數據!AN105 = "", "", [1]攻守數據!AN105)</f>
-        <v>一般</v>
+        <v>水</v>
       </c>
       <c r="D104" s="13" t="str">
         <f>IF([1]攻守數據!AO105 = "", "", [1]攻守數據!AO105)</f>
@@ -7409,21 +7418,21 @@
       </c>
       <c r="E104" s="13">
         <f>IF([1]攻守數據!AP105 = "", "", [1]攻守數據!AP105)</f>
-        <v>94</v>
+        <v>174</v>
       </c>
       <c r="F104" s="13" t="str">
         <f>IF([1]攻守數據!AQ105 = "", "", [1]攻守數據!AQ105)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B105" s="13" t="str">
         <f>IF([1]攻守數據!AM106 = "", "", [1]攻守數據!AM106)</f>
-        <v>水伊布</v>
+        <v>雷伊布</v>
       </c>
       <c r="C105" s="13" t="str">
         <f>IF([1]攻守數據!AN106 = "", "", [1]攻守數據!AN106)</f>
-        <v>水</v>
+        <v>電</v>
       </c>
       <c r="D105" s="13" t="str">
         <f>IF([1]攻守數據!AO106 = "", "", [1]攻守數據!AO106)</f>
@@ -7431,7 +7440,7 @@
       </c>
       <c r="E105" s="13">
         <f>IF([1]攻守數據!AP106 = "", "", [1]攻守數據!AP106)</f>
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F105" s="13" t="str">
         <f>IF([1]攻守數據!AQ106 = "", "", [1]攻守數據!AQ106)</f>
@@ -7441,11 +7450,11 @@
     <row r="106" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B106" s="13" t="str">
         <f>IF([1]攻守數據!AM107 = "", "", [1]攻守數據!AM107)</f>
-        <v>雷伊布</v>
+        <v>火伊布</v>
       </c>
       <c r="C106" s="13" t="str">
         <f>IF([1]攻守數據!AN107 = "", "", [1]攻守數據!AN107)</f>
-        <v>電</v>
+        <v>火</v>
       </c>
       <c r="D106" s="13" t="str">
         <f>IF([1]攻守數據!AO107 = "", "", [1]攻守數據!AO107)</f>
@@ -7453,7 +7462,7 @@
       </c>
       <c r="E106" s="13">
         <f>IF([1]攻守數據!AP107 = "", "", [1]攻守數據!AP107)</f>
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="F106" s="13" t="str">
         <f>IF([1]攻守數據!AQ107 = "", "", [1]攻守數據!AQ107)</f>
@@ -7463,11 +7472,11 @@
     <row r="107" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B107" s="13" t="str">
         <f>IF([1]攻守數據!AM108 = "", "", [1]攻守數據!AM108)</f>
-        <v>火伊布</v>
+        <v>太陽伊布</v>
       </c>
       <c r="C107" s="13" t="str">
         <f>IF([1]攻守數據!AN108 = "", "", [1]攻守數據!AN108)</f>
-        <v>火</v>
+        <v>超能力</v>
       </c>
       <c r="D107" s="13" t="str">
         <f>IF([1]攻守數據!AO108 = "", "", [1]攻守數據!AO108)</f>
@@ -7475,7 +7484,7 @@
       </c>
       <c r="E107" s="13">
         <f>IF([1]攻守數據!AP108 = "", "", [1]攻守數據!AP108)</f>
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="F107" s="13" t="str">
         <f>IF([1]攻守數據!AQ108 = "", "", [1]攻守數據!AQ108)</f>
@@ -7485,11 +7494,11 @@
     <row r="108" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B108" s="13" t="str">
         <f>IF([1]攻守數據!AM109 = "", "", [1]攻守數據!AM109)</f>
-        <v>太陽伊布</v>
+        <v>月亮伊布</v>
       </c>
       <c r="C108" s="13" t="str">
         <f>IF([1]攻守數據!AN109 = "", "", [1]攻守數據!AN109)</f>
-        <v>超能力</v>
+        <v>惡</v>
       </c>
       <c r="D108" s="13" t="str">
         <f>IF([1]攻守數據!AO109 = "", "", [1]攻守數據!AO109)</f>
@@ -7497,7 +7506,7 @@
       </c>
       <c r="E108" s="13">
         <f>IF([1]攻守數據!AP109 = "", "", [1]攻守數據!AP109)</f>
-        <v>218</v>
+        <v>111</v>
       </c>
       <c r="F108" s="13" t="str">
         <f>IF([1]攻守數據!AQ109 = "", "", [1]攻守數據!AQ109)</f>
@@ -7507,11 +7516,11 @@
     <row r="109" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B109" s="13" t="str">
         <f>IF([1]攻守數據!AM110 = "", "", [1]攻守數據!AM110)</f>
-        <v>月亮伊布</v>
+        <v>葉伊布</v>
       </c>
       <c r="C109" s="13" t="str">
         <f>IF([1]攻守數據!AN110 = "", "", [1]攻守數據!AN110)</f>
-        <v>惡</v>
+        <v>草</v>
       </c>
       <c r="D109" s="13" t="str">
         <f>IF([1]攻守數據!AO110 = "", "", [1]攻守數據!AO110)</f>
@@ -7519,7 +7528,7 @@
       </c>
       <c r="E109" s="13">
         <f>IF([1]攻守數據!AP110 = "", "", [1]攻守數據!AP110)</f>
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="F109" s="13" t="str">
         <f>IF([1]攻守數據!AQ110 = "", "", [1]攻守數據!AQ110)</f>
@@ -7529,11 +7538,11 @@
     <row r="110" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B110" s="13" t="str">
         <f>IF([1]攻守數據!AM111 = "", "", [1]攻守數據!AM111)</f>
-        <v>葉伊布</v>
+        <v>冰伊布</v>
       </c>
       <c r="C110" s="13" t="str">
         <f>IF([1]攻守數據!AN111 = "", "", [1]攻守數據!AN111)</f>
-        <v>草</v>
+        <v>冰</v>
       </c>
       <c r="D110" s="13" t="str">
         <f>IF([1]攻守數據!AO111 = "", "", [1]攻守數據!AO111)</f>
@@ -7541,7 +7550,7 @@
       </c>
       <c r="E110" s="13">
         <f>IF([1]攻守數據!AP111 = "", "", [1]攻守數據!AP111)</f>
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="F110" s="13" t="str">
         <f>IF([1]攻守數據!AQ111 = "", "", [1]攻守數據!AQ111)</f>
@@ -7551,11 +7560,11 @@
     <row r="111" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B111" s="13" t="str">
         <f>IF([1]攻守數據!AM112 = "", "", [1]攻守數據!AM112)</f>
-        <v>冰伊布</v>
+        <v>仙子伊布</v>
       </c>
       <c r="C111" s="13" t="str">
         <f>IF([1]攻守數據!AN112 = "", "", [1]攻守數據!AN112)</f>
-        <v>冰</v>
+        <v>妖精</v>
       </c>
       <c r="D111" s="13" t="str">
         <f>IF([1]攻守數據!AO112 = "", "", [1]攻守數據!AO112)</f>
@@ -7563,7 +7572,7 @@
       </c>
       <c r="E111" s="13">
         <f>IF([1]攻守數據!AP112 = "", "", [1]攻守數據!AP112)</f>
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="F111" s="13" t="str">
         <f>IF([1]攻守數據!AQ112 = "", "", [1]攻守數據!AQ112)</f>
@@ -7573,11 +7582,11 @@
     <row r="112" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B112" s="13" t="str">
         <f>IF([1]攻守數據!AM113 = "", "", [1]攻守數據!AM113)</f>
-        <v>仙子伊布</v>
+        <v>艾路雷朵</v>
       </c>
       <c r="C112" s="13" t="str">
         <f>IF([1]攻守數據!AN113 = "", "", [1]攻守數據!AN113)</f>
-        <v>妖精</v>
+        <v>格鬥</v>
       </c>
       <c r="D112" s="13" t="str">
         <f>IF([1]攻守數據!AO113 = "", "", [1]攻守數據!AO113)</f>
@@ -7585,7 +7594,7 @@
       </c>
       <c r="E112" s="13">
         <f>IF([1]攻守數據!AP113 = "", "", [1]攻守數據!AP113)</f>
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="F112" s="13" t="str">
         <f>IF([1]攻守數據!AQ113 = "", "", [1]攻守數據!AQ113)</f>
@@ -7599,7 +7608,7 @@
       </c>
       <c r="C113" s="13" t="str">
         <f>IF([1]攻守數據!AN114 = "", "", [1]攻守數據!AN114)</f>
-        <v>格鬥</v>
+        <v>超能力</v>
       </c>
       <c r="D113" s="13" t="str">
         <f>IF([1]攻守數據!AO114 = "", "", [1]攻守數據!AO114)</f>
@@ -7621,11 +7630,11 @@
       </c>
       <c r="C114" s="13" t="str">
         <f>IF([1]攻守數據!AN115 = "", "", [1]攻守數據!AN115)</f>
-        <v>超能力</v>
+        <v>妖精</v>
       </c>
       <c r="D114" s="13" t="str">
         <f>IF([1]攻守數據!AO115 = "", "", [1]攻守數據!AO115)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E114" s="13">
         <f>IF([1]攻守數據!AP115 = "", "", [1]攻守數據!AP115)</f>
@@ -7639,19 +7648,19 @@
     <row r="115" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B115" s="13" t="str">
         <f>IF([1]攻守數據!AM116 = "", "", [1]攻守數據!AM116)</f>
-        <v>艾路雷朵</v>
+        <v>烏賊王</v>
       </c>
       <c r="C115" s="13" t="str">
         <f>IF([1]攻守數據!AN116 = "", "", [1]攻守數據!AN116)</f>
-        <v>妖精</v>
+        <v>超能力</v>
       </c>
       <c r="D115" s="13" t="str">
         <f>IF([1]攻守數據!AO116 = "", "", [1]攻守數據!AO116)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E115" s="13">
         <f>IF([1]攻守數據!AP116 = "", "", [1]攻守數據!AP116)</f>
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="F115" s="13" t="str">
         <f>IF([1]攻守數據!AQ116 = "", "", [1]攻守數據!AQ116)</f>
@@ -7665,11 +7674,11 @@
       </c>
       <c r="C116" s="13" t="str">
         <f>IF([1]攻守數據!AN117 = "", "", [1]攻守數據!AN117)</f>
-        <v>超能力</v>
+        <v>飛行</v>
       </c>
       <c r="D116" s="13" t="str">
         <f>IF([1]攻守數據!AO117 = "", "", [1]攻守數據!AO117)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E116" s="13">
         <f>IF([1]攻守數據!AP117 = "", "", [1]攻守數據!AP117)</f>
@@ -7683,19 +7692,19 @@
     <row r="117" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B117" s="13" t="str">
         <f>IF([1]攻守數據!AM118 = "", "", [1]攻守數據!AM118)</f>
-        <v>烏賊王</v>
+        <v>洛奇亞</v>
       </c>
       <c r="C117" s="13" t="str">
         <f>IF([1]攻守數據!AN118 = "", "", [1]攻守數據!AN118)</f>
-        <v>飛行</v>
+        <v>超能力</v>
       </c>
       <c r="D117" s="13" t="str">
         <f>IF([1]攻守數據!AO118 = "", "", [1]攻守數據!AO118)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E117" s="13">
         <f>IF([1]攻守數據!AP118 = "", "", [1]攻守數據!AP118)</f>
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F117" s="13" t="str">
         <f>IF([1]攻守數據!AQ118 = "", "", [1]攻守數據!AQ118)</f>
@@ -7709,11 +7718,11 @@
       </c>
       <c r="C118" s="13" t="str">
         <f>IF([1]攻守數據!AN119 = "", "", [1]攻守數據!AN119)</f>
-        <v>超能力</v>
+        <v>龍</v>
       </c>
       <c r="D118" s="13" t="str">
         <f>IF([1]攻守數據!AO119 = "", "", [1]攻守數據!AO119)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E118" s="13">
         <f>IF([1]攻守數據!AP119 = "", "", [1]攻守數據!AP119)</f>
@@ -7727,19 +7736,19 @@
     <row r="119" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B119" s="13" t="str">
         <f>IF([1]攻守數據!AM120 = "", "", [1]攻守數據!AM120)</f>
-        <v>洛奇亞</v>
+        <v>飛腿郎</v>
       </c>
       <c r="C119" s="13" t="str">
         <f>IF([1]攻守數據!AN120 = "", "", [1]攻守數據!AN120)</f>
-        <v>龍</v>
+        <v>格鬥</v>
       </c>
       <c r="D119" s="13" t="str">
         <f>IF([1]攻守數據!AO120 = "", "", [1]攻守數據!AO120)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E119" s="13">
         <f>IF([1]攻守數據!AP120 = "", "", [1]攻守數據!AP120)</f>
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="F119" s="13" t="str">
         <f>IF([1]攻守數據!AQ120 = "", "", [1]攻守數據!AQ120)</f>
@@ -7749,7 +7758,7 @@
     <row r="120" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B120" s="13" t="str">
         <f>IF([1]攻守數據!AM121 = "", "", [1]攻守數據!AM121)</f>
-        <v>飛腿郎</v>
+        <v>快拳郎</v>
       </c>
       <c r="C120" s="13" t="str">
         <f>IF([1]攻守數據!AN121 = "", "", [1]攻守數據!AN121)</f>
@@ -7761,7 +7770,7 @@
       </c>
       <c r="E120" s="13">
         <f>IF([1]攻守數據!AP121 = "", "", [1]攻守數據!AP121)</f>
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="F120" s="13" t="str">
         <f>IF([1]攻守數據!AQ121 = "", "", [1]攻守數據!AQ121)</f>
@@ -7775,11 +7784,11 @@
       </c>
       <c r="C121" s="13" t="str">
         <f>IF([1]攻守數據!AN122 = "", "", [1]攻守數據!AN122)</f>
-        <v>格鬥</v>
+        <v>鋼</v>
       </c>
       <c r="D121" s="13" t="str">
         <f>IF([1]攻守數據!AO122 = "", "", [1]攻守數據!AO122)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E121" s="13">
         <f>IF([1]攻守數據!AP122 = "", "", [1]攻守數據!AP122)</f>
@@ -7793,19 +7802,19 @@
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B122" s="13" t="str">
         <f>IF([1]攻守數據!AM123 = "", "", [1]攻守數據!AM123)</f>
-        <v>快拳郎</v>
+        <v>帝牙海獅</v>
       </c>
       <c r="C122" s="13" t="str">
         <f>IF([1]攻守數據!AN123 = "", "", [1]攻守數據!AN123)</f>
-        <v>鋼</v>
+        <v>冰</v>
       </c>
       <c r="D122" s="13" t="str">
         <f>IF([1]攻守數據!AO123 = "", "", [1]攻守數據!AO123)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E122" s="13">
         <f>IF([1]攻守數據!AP123 = "", "", [1]攻守數據!AP123)</f>
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F122" s="13" t="str">
         <f>IF([1]攻守數據!AQ123 = "", "", [1]攻守數據!AQ123)</f>
@@ -7815,11 +7824,11 @@
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B123" s="13" t="str">
         <f>IF([1]攻守數據!AM124 = "", "", [1]攻守數據!AM124)</f>
-        <v>帝牙海獅</v>
+        <v>龐岩怪</v>
       </c>
       <c r="C123" s="13" t="str">
         <f>IF([1]攻守數據!AN124 = "", "", [1]攻守數據!AN124)</f>
-        <v>水</v>
+        <v>岩石</v>
       </c>
       <c r="D123" s="13" t="str">
         <f>IF([1]攻守數據!AO124 = "", "", [1]攻守數據!AO124)</f>
@@ -7827,7 +7836,7 @@
       </c>
       <c r="E123" s="13">
         <f>IF([1]攻守數據!AP124 = "", "", [1]攻守數據!AP124)</f>
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="F123" s="13" t="str">
         <f>IF([1]攻守數據!AQ124 = "", "", [1]攻守數據!AQ124)</f>
@@ -7837,11 +7846,11 @@
     <row r="124" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B124" s="13" t="str">
         <f>IF([1]攻守數據!AM125 = "", "", [1]攻守數據!AM125)</f>
-        <v>帝牙海獅</v>
+        <v>龐岩怪</v>
       </c>
       <c r="C124" s="13" t="str">
         <f>IF([1]攻守數據!AN125 = "", "", [1]攻守數據!AN125)</f>
-        <v>冰</v>
+        <v>地面</v>
       </c>
       <c r="D124" s="13" t="str">
         <f>IF([1]攻守數據!AO125 = "", "", [1]攻守數據!AO125)</f>
@@ -7849,7 +7858,7 @@
       </c>
       <c r="E124" s="13">
         <f>IF([1]攻守數據!AP125 = "", "", [1]攻守數據!AP125)</f>
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="F124" s="13" t="str">
         <f>IF([1]攻守數據!AQ125 = "", "", [1]攻守數據!AQ125)</f>
@@ -7859,19 +7868,19 @@
     <row r="125" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B125" s="13" t="str">
         <f>IF([1]攻守數據!AM126 = "", "", [1]攻守數據!AM126)</f>
-        <v>龐岩怪</v>
+        <v>老翁龍</v>
       </c>
       <c r="C125" s="13" t="str">
         <f>IF([1]攻守數據!AN126 = "", "", [1]攻守數據!AN126)</f>
-        <v>岩石</v>
+        <v>龍</v>
       </c>
       <c r="D125" s="13" t="str">
         <f>IF([1]攻守數據!AO126 = "", "", [1]攻守數據!AO126)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E125" s="13">
         <f>IF([1]攻守數據!AP126 = "", "", [1]攻守數據!AP126)</f>
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F125" s="13" t="str">
         <f>IF([1]攻守數據!AQ126 = "", "", [1]攻守數據!AQ126)</f>
@@ -7881,19 +7890,19 @@
     <row r="126" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B126" s="13" t="str">
         <f>IF([1]攻守數據!AM127 = "", "", [1]攻守數據!AM127)</f>
-        <v>龐岩怪</v>
+        <v>老翁龍</v>
       </c>
       <c r="C126" s="13" t="str">
         <f>IF([1]攻守數據!AN127 = "", "", [1]攻守數據!AN127)</f>
-        <v>地面</v>
+        <v>超能力</v>
       </c>
       <c r="D126" s="13" t="str">
         <f>IF([1]攻守數據!AO127 = "", "", [1]攻守數據!AO127)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E126" s="13">
         <f>IF([1]攻守數據!AP127 = "", "", [1]攻守數據!AP127)</f>
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F126" s="13" t="str">
         <f>IF([1]攻守數據!AQ127 = "", "", [1]攻守數據!AQ127)</f>
@@ -7903,19 +7912,19 @@
     <row r="127" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B127" s="13" t="str">
         <f>IF([1]攻守數據!AM128 = "", "", [1]攻守數據!AM128)</f>
-        <v>老翁龍</v>
+        <v>鳳王</v>
       </c>
       <c r="C127" s="13" t="str">
         <f>IF([1]攻守數據!AN128 = "", "", [1]攻守數據!AN128)</f>
-        <v>龍</v>
+        <v>火</v>
       </c>
       <c r="D127" s="13" t="str">
         <f>IF([1]攻守數據!AO128 = "", "", [1]攻守數據!AO128)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E127" s="13">
         <f>IF([1]攻守數據!AP128 = "", "", [1]攻守數據!AP128)</f>
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F127" s="13" t="str">
         <f>IF([1]攻守數據!AQ128 = "", "", [1]攻守數據!AQ128)</f>
@@ -7925,7 +7934,7 @@
     <row r="128" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B128" s="13" t="str">
         <f>IF([1]攻守數據!AM129 = "", "", [1]攻守數據!AM129)</f>
-        <v>老翁龍</v>
+        <v>鳳王</v>
       </c>
       <c r="C128" s="13" t="str">
         <f>IF([1]攻守數據!AN129 = "", "", [1]攻守數據!AN129)</f>
@@ -7933,11 +7942,11 @@
       </c>
       <c r="D128" s="13" t="str">
         <f>IF([1]攻守數據!AO129 = "", "", [1]攻守數據!AO129)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E128" s="13">
         <f>IF([1]攻守數據!AP129 = "", "", [1]攻守數據!AP129)</f>
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F128" s="13" t="str">
         <f>IF([1]攻守數據!AQ129 = "", "", [1]攻守數據!AQ129)</f>
@@ -7951,11 +7960,11 @@
       </c>
       <c r="C129" s="13" t="str">
         <f>IF([1]攻守數據!AN130 = "", "", [1]攻守數據!AN130)</f>
-        <v>火</v>
+        <v>一般</v>
       </c>
       <c r="D129" s="13" t="str">
         <f>IF([1]攻守數據!AO130 = "", "", [1]攻守數據!AO130)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E129" s="13">
         <f>IF([1]攻守數據!AP130 = "", "", [1]攻守數據!AP130)</f>
@@ -7973,7 +7982,7 @@
       </c>
       <c r="C130" s="13" t="str">
         <f>IF([1]攻守數據!AN131 = "", "", [1]攻守數據!AN131)</f>
-        <v>超能力</v>
+        <v>鋼</v>
       </c>
       <c r="D130" s="13" t="str">
         <f>IF([1]攻守數據!AO131 = "", "", [1]攻守數據!AO131)</f>
@@ -7991,11 +8000,11 @@
     <row r="131" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B131" s="13" t="str">
         <f>IF([1]攻守數據!AM132 = "", "", [1]攻守數據!AM132)</f>
-        <v>鳳王</v>
+        <v>風速狗</v>
       </c>
       <c r="C131" s="13" t="str">
         <f>IF([1]攻守數據!AN132 = "", "", [1]攻守數據!AN132)</f>
-        <v>一般</v>
+        <v>火</v>
       </c>
       <c r="D131" s="13" t="str">
         <f>IF([1]攻守數據!AO132 = "", "", [1]攻守數據!AO132)</f>
@@ -8003,7 +8012,7 @@
       </c>
       <c r="E131" s="13">
         <f>IF([1]攻守數據!AP132 = "", "", [1]攻守數據!AP132)</f>
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F131" s="13" t="str">
         <f>IF([1]攻守數據!AQ132 = "", "", [1]攻守數據!AQ132)</f>
@@ -8013,19 +8022,19 @@
     <row r="132" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B132" s="13" t="str">
         <f>IF([1]攻守數據!AM133 = "", "", [1]攻守數據!AM133)</f>
-        <v>鳳王</v>
+        <v>風速狗</v>
       </c>
       <c r="C132" s="13" t="str">
         <f>IF([1]攻守數據!AN133 = "", "", [1]攻守數據!AN133)</f>
-        <v>鋼</v>
+        <v>惡</v>
       </c>
       <c r="D132" s="13" t="str">
         <f>IF([1]攻守數據!AO133 = "", "", [1]攻守數據!AO133)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E132" s="13">
         <f>IF([1]攻守數據!AP133 = "", "", [1]攻守數據!AP133)</f>
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F132" s="13" t="str">
         <f>IF([1]攻守數據!AQ133 = "", "", [1]攻守數據!AQ133)</f>
@@ -8039,11 +8048,11 @@
       </c>
       <c r="C133" s="13" t="str">
         <f>IF([1]攻守數據!AN134 = "", "", [1]攻守數據!AN134)</f>
-        <v>火</v>
+        <v>電</v>
       </c>
       <c r="D133" s="13" t="str">
         <f>IF([1]攻守數據!AO134 = "", "", [1]攻守數據!AO134)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E133" s="13">
         <f>IF([1]攻守數據!AP134 = "", "", [1]攻守數據!AP134)</f>
@@ -8057,11 +8066,11 @@
     <row r="134" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B134" s="13" t="str">
         <f>IF([1]攻守數據!AM135 = "", "", [1]攻守數據!AM135)</f>
-        <v>風速狗</v>
+        <v>喵喵</v>
       </c>
       <c r="C134" s="13" t="str">
         <f>IF([1]攻守數據!AN135 = "", "", [1]攻守數據!AN135)</f>
-        <v>惡</v>
+        <v>一般</v>
       </c>
       <c r="D134" s="13" t="str">
         <f>IF([1]攻守數據!AO135 = "", "", [1]攻守數據!AO135)</f>
@@ -8069,7 +8078,7 @@
       </c>
       <c r="E134" s="13">
         <f>IF([1]攻守數據!AP135 = "", "", [1]攻守數據!AP135)</f>
-        <v>191</v>
+        <v>85</v>
       </c>
       <c r="F134" s="13" t="str">
         <f>IF([1]攻守數據!AQ135 = "", "", [1]攻守數據!AQ135)</f>
@@ -8079,7 +8088,7 @@
     <row r="135" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B135" s="13" t="str">
         <f>IF([1]攻守數據!AM136 = "", "", [1]攻守數據!AM136)</f>
-        <v>風速狗</v>
+        <v>超極巨喵喵</v>
       </c>
       <c r="C135" s="13" t="str">
         <f>IF([1]攻守數據!AN136 = "", "", [1]攻守數據!AN136)</f>
@@ -8087,25 +8096,25 @@
       </c>
       <c r="D135" s="13" t="str">
         <f>IF([1]攻守數據!AO136 = "", "", [1]攻守數據!AO136)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E135" s="13">
         <f>IF([1]攻守數據!AP136 = "", "", [1]攻守數據!AP136)</f>
-        <v>191</v>
+        <v>85</v>
       </c>
       <c r="F135" s="13" t="str">
         <f>IF([1]攻守數據!AQ136 = "", "", [1]攻守數據!AQ136)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B136" s="13" t="str">
         <f>IF([1]攻守數據!AM137 = "", "", [1]攻守數據!AM137)</f>
-        <v>超極巨喵喵</v>
+        <v>超極巨皮卡丘</v>
       </c>
       <c r="C136" s="13" t="str">
         <f>IF([1]攻守數據!AN137 = "", "", [1]攻守數據!AN137)</f>
-        <v>一般</v>
+        <v>電</v>
       </c>
       <c r="D136" s="13" t="str">
         <f>IF([1]攻守數據!AO137 = "", "", [1]攻守數據!AO137)</f>
@@ -8113,7 +8122,7 @@
       </c>
       <c r="E136" s="13">
         <f>IF([1]攻守數據!AP137 = "", "", [1]攻守數據!AP137)</f>
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F136" s="13" t="str">
         <f>IF([1]攻守數據!AQ137 = "", "", [1]攻守數據!AQ137)</f>
@@ -8123,11 +8132,11 @@
     <row r="137" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B137" s="13" t="str">
         <f>IF([1]攻守數據!AM138 = "", "", [1]攻守數據!AM138)</f>
-        <v>超極巨皮卡丘</v>
+        <v>雷丘</v>
       </c>
       <c r="C137" s="13" t="str">
         <f>IF([1]攻守數據!AN138 = "", "", [1]攻守數據!AN138)</f>
-        <v>電</v>
+        <v>妖精</v>
       </c>
       <c r="D137" s="13" t="str">
         <f>IF([1]攻守數據!AO138 = "", "", [1]攻守數據!AO138)</f>
@@ -8135,21 +8144,21 @@
       </c>
       <c r="E137" s="13">
         <f>IF([1]攻守數據!AP138 = "", "", [1]攻守數據!AP138)</f>
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="F137" s="13" t="str">
         <f>IF([1]攻守數據!AQ138 = "", "", [1]攻守數據!AQ138)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B138" s="13" t="str">
         <f>IF([1]攻守數據!AM139 = "", "", [1]攻守數據!AM139)</f>
-        <v>雷丘</v>
+        <v>雷吉艾斯</v>
       </c>
       <c r="C138" s="13" t="str">
         <f>IF([1]攻守數據!AN139 = "", "", [1]攻守數據!AN139)</f>
-        <v>電</v>
+        <v>冰</v>
       </c>
       <c r="D138" s="13" t="str">
         <f>IF([1]攻守數據!AO139 = "", "", [1]攻守數據!AO139)</f>
@@ -8157,7 +8166,7 @@
       </c>
       <c r="E138" s="13">
         <f>IF([1]攻守數據!AP139 = "", "", [1]攻守數據!AP139)</f>
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="F138" s="13" t="str">
         <f>IF([1]攻守數據!AQ139 = "", "", [1]攻守數據!AQ139)</f>
@@ -8167,11 +8176,11 @@
     <row r="139" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B139" s="13" t="str">
         <f>IF([1]攻守數據!AM140 = "", "", [1]攻守數據!AM140)</f>
-        <v>雷丘</v>
+        <v>雷吉艾斯</v>
       </c>
       <c r="C139" s="13" t="str">
         <f>IF([1]攻守數據!AN140 = "", "", [1]攻守數據!AN140)</f>
-        <v>妖精</v>
+        <v>一般</v>
       </c>
       <c r="D139" s="13" t="str">
         <f>IF([1]攻守數據!AO140 = "", "", [1]攻守數據!AO140)</f>
@@ -8179,7 +8188,7 @@
       </c>
       <c r="E139" s="13">
         <f>IF([1]攻守數據!AP140 = "", "", [1]攻守數據!AP140)</f>
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="F139" s="13" t="str">
         <f>IF([1]攻守數據!AQ140 = "", "", [1]攻守數據!AQ140)</f>
@@ -8193,11 +8202,11 @@
       </c>
       <c r="C140" s="13" t="str">
         <f>IF([1]攻守數據!AN141 = "", "", [1]攻守數據!AN141)</f>
-        <v>冰</v>
+        <v>格鬥</v>
       </c>
       <c r="D140" s="13" t="str">
         <f>IF([1]攻守數據!AO141 = "", "", [1]攻守數據!AO141)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E140" s="13">
         <f>IF([1]攻守數據!AP141 = "", "", [1]攻守數據!AP141)</f>
@@ -8211,11 +8220,11 @@
     <row r="141" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B141" s="13" t="str">
         <f>IF([1]攻守數據!AM142 = "", "", [1]攻守數據!AM142)</f>
-        <v>雷吉艾斯</v>
+        <v>沙漠蜻蜓</v>
       </c>
       <c r="C141" s="13" t="str">
         <f>IF([1]攻守數據!AN142 = "", "", [1]攻守數據!AN142)</f>
-        <v>一般</v>
+        <v>地面</v>
       </c>
       <c r="D141" s="13" t="str">
         <f>IF([1]攻守數據!AO142 = "", "", [1]攻守數據!AO142)</f>
@@ -8223,7 +8232,7 @@
       </c>
       <c r="E141" s="13">
         <f>IF([1]攻守數據!AP142 = "", "", [1]攻守數據!AP142)</f>
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="F141" s="13" t="str">
         <f>IF([1]攻守數據!AQ142 = "", "", [1]攻守數據!AQ142)</f>
@@ -8233,19 +8242,19 @@
     <row r="142" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B142" s="13" t="str">
         <f>IF([1]攻守數據!AM143 = "", "", [1]攻守數據!AM143)</f>
-        <v>雷吉艾斯</v>
+        <v>沙漠蜻蜓</v>
       </c>
       <c r="C142" s="13" t="str">
         <f>IF([1]攻守數據!AN143 = "", "", [1]攻守數據!AN143)</f>
-        <v>格鬥</v>
+        <v>龍</v>
       </c>
       <c r="D142" s="13" t="str">
         <f>IF([1]攻守數據!AO143 = "", "", [1]攻守數據!AO143)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E142" s="13">
         <f>IF([1]攻守數據!AP143 = "", "", [1]攻守數據!AP143)</f>
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="F142" s="13" t="str">
         <f>IF([1]攻守數據!AQ143 = "", "", [1]攻守數據!AQ143)</f>
@@ -8255,11 +8264,11 @@
     <row r="143" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B143" s="13" t="str">
         <f>IF([1]攻守數據!AM144 = "", "", [1]攻守數據!AM144)</f>
-        <v>沙漠蜻蜓</v>
+        <v>雷吉洛克</v>
       </c>
       <c r="C143" s="13" t="str">
         <f>IF([1]攻守數據!AN144 = "", "", [1]攻守數據!AN144)</f>
-        <v>地面</v>
+        <v>岩石</v>
       </c>
       <c r="D143" s="13" t="str">
         <f>IF([1]攻守數據!AO144 = "", "", [1]攻守數據!AO144)</f>
@@ -8267,7 +8276,7 @@
       </c>
       <c r="E143" s="13">
         <f>IF([1]攻守數據!AP144 = "", "", [1]攻守數據!AP144)</f>
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="F143" s="13" t="str">
         <f>IF([1]攻守數據!AQ144 = "", "", [1]攻守數據!AQ144)</f>
@@ -8277,11 +8286,11 @@
     <row r="144" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B144" s="13" t="str">
         <f>IF([1]攻守數據!AM145 = "", "", [1]攻守數據!AM145)</f>
-        <v>沙漠蜻蜓</v>
+        <v>雷吉洛克</v>
       </c>
       <c r="C144" s="13" t="str">
         <f>IF([1]攻守數據!AN145 = "", "", [1]攻守數據!AN145)</f>
-        <v>龍</v>
+        <v>一般</v>
       </c>
       <c r="D144" s="13" t="str">
         <f>IF([1]攻守數據!AO145 = "", "", [1]攻守數據!AO145)</f>
@@ -8289,7 +8298,7 @@
       </c>
       <c r="E144" s="13">
         <f>IF([1]攻守數據!AP145 = "", "", [1]攻守數據!AP145)</f>
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="F144" s="13" t="str">
         <f>IF([1]攻守數據!AQ145 = "", "", [1]攻守數據!AQ145)</f>
@@ -8303,11 +8312,11 @@
       </c>
       <c r="C145" s="13" t="str">
         <f>IF([1]攻守數據!AN146 = "", "", [1]攻守數據!AN146)</f>
-        <v>岩石</v>
+        <v>格鬥</v>
       </c>
       <c r="D145" s="13" t="str">
         <f>IF([1]攻守數據!AO146 = "", "", [1]攻守數據!AO146)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E145" s="13">
         <f>IF([1]攻守數據!AP146 = "", "", [1]攻守數據!AP146)</f>
@@ -8321,11 +8330,11 @@
     <row r="146" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B146" s="13" t="str">
         <f>IF([1]攻守數據!AM147 = "", "", [1]攻守數據!AM147)</f>
-        <v>雷吉洛克</v>
+        <v>雷吉斯奇魯</v>
       </c>
       <c r="C146" s="13" t="str">
         <f>IF([1]攻守數據!AN147 = "", "", [1]攻守數據!AN147)</f>
-        <v>一般</v>
+        <v>鋼</v>
       </c>
       <c r="D146" s="13" t="str">
         <f>IF([1]攻守數據!AO147 = "", "", [1]攻守數據!AO147)</f>
@@ -8333,7 +8342,7 @@
       </c>
       <c r="E146" s="13">
         <f>IF([1]攻守數據!AP147 = "", "", [1]攻守數據!AP147)</f>
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="F146" s="13" t="str">
         <f>IF([1]攻守數據!AQ147 = "", "", [1]攻守數據!AQ147)</f>
@@ -8343,19 +8352,19 @@
     <row r="147" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B147" s="13" t="str">
         <f>IF([1]攻守數據!AM148 = "", "", [1]攻守數據!AM148)</f>
-        <v>雷吉洛克</v>
+        <v>雷吉斯奇魯</v>
       </c>
       <c r="C147" s="13" t="str">
         <f>IF([1]攻守數據!AN148 = "", "", [1]攻守數據!AN148)</f>
-        <v>格鬥</v>
+        <v>一般</v>
       </c>
       <c r="D147" s="13" t="str">
         <f>IF([1]攻守數據!AO148 = "", "", [1]攻守數據!AO148)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E147" s="13">
         <f>IF([1]攻守數據!AP148 = "", "", [1]攻守數據!AP148)</f>
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="F147" s="13" t="str">
         <f>IF([1]攻守數據!AQ148 = "", "", [1]攻守數據!AQ148)</f>
@@ -8369,11 +8378,11 @@
       </c>
       <c r="C148" s="13" t="str">
         <f>IF([1]攻守數據!AN149 = "", "", [1]攻守數據!AN149)</f>
-        <v>鋼</v>
+        <v>格鬥</v>
       </c>
       <c r="D148" s="13" t="str">
         <f>IF([1]攻守數據!AO149 = "", "", [1]攻守數據!AO149)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E148" s="13">
         <f>IF([1]攻守數據!AP149 = "", "", [1]攻守數據!AP149)</f>
@@ -8387,11 +8396,11 @@
     <row r="149" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B149" s="13" t="str">
         <f>IF([1]攻守數據!AM150 = "", "", [1]攻守數據!AM150)</f>
-        <v>雷吉斯奇魯</v>
+        <v>長毛巨魔</v>
       </c>
       <c r="C149" s="13" t="str">
         <f>IF([1]攻守數據!AN150 = "", "", [1]攻守數據!AN150)</f>
-        <v>一般</v>
+        <v>惡</v>
       </c>
       <c r="D149" s="13" t="str">
         <f>IF([1]攻守數據!AO150 = "", "", [1]攻守數據!AO150)</f>
@@ -8399,7 +8408,7 @@
       </c>
       <c r="E149" s="13">
         <f>IF([1]攻守數據!AP150 = "", "", [1]攻守數據!AP150)</f>
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="F149" s="13" t="str">
         <f>IF([1]攻守數據!AQ150 = "", "", [1]攻守數據!AQ150)</f>
@@ -8409,33 +8418,33 @@
     <row r="150" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B150" s="13" t="str">
         <f>IF([1]攻守數據!AM151 = "", "", [1]攻守數據!AM151)</f>
-        <v>雷吉斯奇魯</v>
+        <v>超極巨長毛巨魔</v>
       </c>
       <c r="C150" s="13" t="str">
         <f>IF([1]攻守數據!AN151 = "", "", [1]攻守數據!AN151)</f>
-        <v>格鬥</v>
+        <v>草</v>
       </c>
       <c r="D150" s="13" t="str">
         <f>IF([1]攻守數據!AO151 = "", "", [1]攻守數據!AO151)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E150" s="13">
         <f>IF([1]攻守數據!AP151 = "", "", [1]攻守數據!AP151)</f>
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="F150" s="13" t="str">
         <f>IF([1]攻守數據!AQ151 = "", "", [1]攻守數據!AQ151)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B151" s="13" t="str">
         <f>IF([1]攻守數據!AM152 = "", "", [1]攻守數據!AM152)</f>
-        <v>超極巨長毛巨魔</v>
+        <v>風妖精</v>
       </c>
       <c r="C151" s="13" t="str">
         <f>IF([1]攻守數據!AN152 = "", "", [1]攻守數據!AN152)</f>
-        <v>惡</v>
+        <v>妖精</v>
       </c>
       <c r="D151" s="13" t="str">
         <f>IF([1]攻守數據!AO152 = "", "", [1]攻守數據!AO152)</f>
@@ -8443,21 +8452,21 @@
       </c>
       <c r="E151" s="13">
         <f>IF([1]攻守數據!AP152 = "", "", [1]攻守數據!AP152)</f>
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="F151" s="13" t="str">
         <f>IF([1]攻守數據!AQ152 = "", "", [1]攻守數據!AQ152)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B152" s="13" t="str">
         <f>IF([1]攻守數據!AM153 = "", "", [1]攻守數據!AM153)</f>
-        <v>風妖精</v>
+        <v>蜂女王</v>
       </c>
       <c r="C152" s="13" t="str">
         <f>IF([1]攻守數據!AN153 = "", "", [1]攻守數據!AN153)</f>
-        <v>草</v>
+        <v>蟲</v>
       </c>
       <c r="D152" s="13" t="str">
         <f>IF([1]攻守數據!AO153 = "", "", [1]攻守數據!AO153)</f>
@@ -8465,7 +8474,7 @@
       </c>
       <c r="E152" s="13">
         <f>IF([1]攻守數據!AP153 = "", "", [1]攻守數據!AP153)</f>
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F152" s="13" t="str">
         <f>IF([1]攻守數據!AQ153 = "", "", [1]攻守數據!AQ153)</f>
@@ -8475,11 +8484,11 @@
     <row r="153" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B153" s="13" t="str">
         <f>IF([1]攻守數據!AM154 = "", "", [1]攻守數據!AM154)</f>
-        <v>風妖精</v>
+        <v>蜂女王</v>
       </c>
       <c r="C153" s="13" t="str">
         <f>IF([1]攻守數據!AN154 = "", "", [1]攻守數據!AN154)</f>
-        <v>妖精</v>
+        <v>飛行</v>
       </c>
       <c r="D153" s="13" t="str">
         <f>IF([1]攻守數據!AO154 = "", "", [1]攻守數據!AO154)</f>
@@ -8487,7 +8496,7 @@
       </c>
       <c r="E153" s="13">
         <f>IF([1]攻守數據!AP154 = "", "", [1]攻守數據!AP154)</f>
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F153" s="13" t="str">
         <f>IF([1]攻守數據!AQ154 = "", "", [1]攻守數據!AQ154)</f>
@@ -8501,7 +8510,7 @@
       </c>
       <c r="C154" s="13" t="str">
         <f>IF([1]攻守數據!AN155 = "", "", [1]攻守數據!AN155)</f>
-        <v>蟲</v>
+        <v>毒</v>
       </c>
       <c r="D154" s="13" t="str">
         <f>IF([1]攻守數據!AO155 = "", "", [1]攻守數據!AO155)</f>
@@ -8519,19 +8528,19 @@
     <row r="155" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B155" s="13" t="str">
         <f>IF([1]攻守數據!AM156 = "", "", [1]攻守數據!AM156)</f>
-        <v>蜂女王</v>
+        <v>電擊魔獸</v>
       </c>
       <c r="C155" s="13" t="str">
         <f>IF([1]攻守數據!AN156 = "", "", [1]攻守數據!AN156)</f>
-        <v>飛行</v>
+        <v>電</v>
       </c>
       <c r="D155" s="13" t="str">
         <f>IF([1]攻守數據!AO156 = "", "", [1]攻守數據!AO156)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E155" s="13">
         <f>IF([1]攻守數據!AP156 = "", "", [1]攻守數據!AP156)</f>
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="F155" s="13" t="str">
         <f>IF([1]攻守數據!AQ156 = "", "", [1]攻守數據!AQ156)</f>
@@ -8541,19 +8550,19 @@
     <row r="156" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B156" s="13" t="str">
         <f>IF([1]攻守數據!AM157 = "", "", [1]攻守數據!AM157)</f>
-        <v>蜂女王</v>
+        <v>電擊魔獸</v>
       </c>
       <c r="C156" s="13" t="str">
         <f>IF([1]攻守數據!AN157 = "", "", [1]攻守數據!AN157)</f>
-        <v>毒</v>
+        <v>格鬥</v>
       </c>
       <c r="D156" s="13" t="str">
         <f>IF([1]攻守數據!AO157 = "", "", [1]攻守數據!AO157)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E156" s="13">
         <f>IF([1]攻守數據!AP157 = "", "", [1]攻守數據!AP157)</f>
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="F156" s="13" t="str">
         <f>IF([1]攻守數據!AQ157 = "", "", [1]攻守數據!AQ157)</f>
@@ -8563,19 +8572,19 @@
     <row r="157" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B157" s="13" t="str">
         <f>IF([1]攻守數據!AM158 = "", "", [1]攻守數據!AM158)</f>
-        <v>電擊魔獸</v>
+        <v>貓頭夜鷹</v>
       </c>
       <c r="C157" s="13" t="str">
         <f>IF([1]攻守數據!AN158 = "", "", [1]攻守數據!AN158)</f>
-        <v>電</v>
+        <v>飛行</v>
       </c>
       <c r="D157" s="13" t="str">
         <f>IF([1]攻守數據!AO158 = "", "", [1]攻守數據!AO158)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E157" s="13">
         <f>IF([1]攻守數據!AP158 = "", "", [1]攻守數據!AP158)</f>
-        <v>209</v>
+        <v>126</v>
       </c>
       <c r="F157" s="13" t="str">
         <f>IF([1]攻守數據!AQ158 = "", "", [1]攻守數據!AQ158)</f>
@@ -8585,19 +8594,19 @@
     <row r="158" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B158" s="13" t="str">
         <f>IF([1]攻守數據!AM159 = "", "", [1]攻守數據!AM159)</f>
-        <v>電擊魔獸</v>
+        <v>貓頭夜鷹</v>
       </c>
       <c r="C158" s="13" t="str">
         <f>IF([1]攻守數據!AN159 = "", "", [1]攻守數據!AN159)</f>
-        <v>格鬥</v>
+        <v>超能力</v>
       </c>
       <c r="D158" s="13" t="str">
         <f>IF([1]攻守數據!AO159 = "", "", [1]攻守數據!AO159)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E158" s="13">
         <f>IF([1]攻守數據!AP159 = "", "", [1]攻守數據!AP159)</f>
-        <v>209</v>
+        <v>126</v>
       </c>
       <c r="F158" s="13" t="str">
         <f>IF([1]攻守數據!AQ159 = "", "", [1]攻守數據!AQ159)</f>
@@ -8607,19 +8616,19 @@
     <row r="159" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B159" s="13" t="str">
         <f>IF([1]攻守數據!AM160 = "", "", [1]攻守數據!AM160)</f>
-        <v>貓頭夜鷹</v>
+        <v>暴鯉龍</v>
       </c>
       <c r="C159" s="13" t="str">
         <f>IF([1]攻守數據!AN160 = "", "", [1]攻守數據!AN160)</f>
-        <v>飛行</v>
+        <v>水</v>
       </c>
       <c r="D159" s="13" t="str">
         <f>IF([1]攻守數據!AO160 = "", "", [1]攻守數據!AO160)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E159" s="13">
         <f>IF([1]攻守數據!AP160 = "", "", [1]攻守數據!AP160)</f>
-        <v>126</v>
+        <v>199</v>
       </c>
       <c r="F159" s="13" t="str">
         <f>IF([1]攻守數據!AQ160 = "", "", [1]攻守數據!AQ160)</f>
@@ -8629,19 +8638,19 @@
     <row r="160" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B160" s="13" t="str">
         <f>IF([1]攻守數據!AM161 = "", "", [1]攻守數據!AM161)</f>
-        <v>貓頭夜鷹</v>
+        <v>暴鯉龍</v>
       </c>
       <c r="C160" s="13" t="str">
         <f>IF([1]攻守數據!AN161 = "", "", [1]攻守數據!AN161)</f>
-        <v>超能力</v>
+        <v>惡</v>
       </c>
       <c r="D160" s="13" t="str">
         <f>IF([1]攻守數據!AO161 = "", "", [1]攻守數據!AO161)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E160" s="13">
         <f>IF([1]攻守數據!AP161 = "", "", [1]攻守數據!AP161)</f>
-        <v>126</v>
+        <v>199</v>
       </c>
       <c r="F160" s="13" t="str">
         <f>IF([1]攻守數據!AQ161 = "", "", [1]攻守數據!AQ161)</f>
@@ -8655,7 +8664,7 @@
       </c>
       <c r="C161" s="13" t="str">
         <f>IF([1]攻守數據!AN162 = "", "", [1]攻守數據!AN162)</f>
-        <v>水</v>
+        <v>龍</v>
       </c>
       <c r="D161" s="13" t="str">
         <f>IF([1]攻守數據!AO162 = "", "", [1]攻守數據!AO162)</f>
@@ -8673,7 +8682,7 @@
     <row r="162" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B162" s="13" t="str">
         <f>IF([1]攻守數據!AM163 = "", "", [1]攻守數據!AM163)</f>
-        <v>暴鯉龍</v>
+        <v>三首惡龍</v>
       </c>
       <c r="C162" s="13" t="str">
         <f>IF([1]攻守數據!AN163 = "", "", [1]攻守數據!AN163)</f>
@@ -8681,11 +8690,11 @@
       </c>
       <c r="D162" s="13" t="str">
         <f>IF([1]攻守數據!AO163 = "", "", [1]攻守數據!AO163)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E162" s="13">
         <f>IF([1]攻守數據!AP163 = "", "", [1]攻守數據!AP163)</f>
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="F162" s="13" t="str">
         <f>IF([1]攻守數據!AQ163 = "", "", [1]攻守數據!AQ163)</f>
@@ -8695,7 +8704,7 @@
     <row r="163" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B163" s="13" t="str">
         <f>IF([1]攻守數據!AM164 = "", "", [1]攻守數據!AM164)</f>
-        <v>暴鯉龍</v>
+        <v>三首惡龍</v>
       </c>
       <c r="C163" s="13" t="str">
         <f>IF([1]攻守數據!AN164 = "", "", [1]攻守數據!AN164)</f>
@@ -8703,11 +8712,11 @@
       </c>
       <c r="D163" s="13" t="str">
         <f>IF([1]攻守數據!AO164 = "", "", [1]攻守數據!AO164)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E163" s="13">
         <f>IF([1]攻守數據!AP164 = "", "", [1]攻守數據!AP164)</f>
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="F163" s="13" t="str">
         <f>IF([1]攻守數據!AQ164 = "", "", [1]攻守數據!AQ164)</f>
@@ -8717,11 +8726,11 @@
     <row r="164" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B164" s="13" t="str">
         <f>IF([1]攻守數據!AM165 = "", "", [1]攻守數據!AM165)</f>
-        <v>三首惡龍</v>
+        <v>美納斯</v>
       </c>
       <c r="C164" s="13" t="str">
         <f>IF([1]攻守數據!AN165 = "", "", [1]攻守數據!AN165)</f>
-        <v>惡</v>
+        <v>水</v>
       </c>
       <c r="D164" s="13" t="str">
         <f>IF([1]攻守數據!AO165 = "", "", [1]攻守數據!AO165)</f>
@@ -8729,7 +8738,7 @@
       </c>
       <c r="E164" s="13">
         <f>IF([1]攻守數據!AP165 = "", "", [1]攻守數據!AP165)</f>
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F164" s="13" t="str">
         <f>IF([1]攻守數據!AQ165 = "", "", [1]攻守數據!AQ165)</f>
@@ -8739,7 +8748,7 @@
     <row r="165" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B165" s="13" t="str">
         <f>IF([1]攻守數據!AM166 = "", "", [1]攻守數據!AM166)</f>
-        <v>三首惡龍</v>
+        <v>美納斯</v>
       </c>
       <c r="C165" s="13" t="str">
         <f>IF([1]攻守數據!AN166 = "", "", [1]攻守數據!AN166)</f>
@@ -8751,7 +8760,7 @@
       </c>
       <c r="E165" s="13">
         <f>IF([1]攻守數據!AP166 = "", "", [1]攻守數據!AP166)</f>
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F165" s="13" t="str">
         <f>IF([1]攻守數據!AQ166 = "", "", [1]攻守數據!AQ166)</f>
@@ -8761,19 +8770,19 @@
     <row r="166" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B166" s="13" t="str">
         <f>IF([1]攻守數據!AM167 = "", "", [1]攻守數據!AM167)</f>
-        <v>美納斯</v>
+        <v>鴨嘴炎獸</v>
       </c>
       <c r="C166" s="13" t="str">
         <f>IF([1]攻守數據!AN167 = "", "", [1]攻守數據!AN167)</f>
-        <v>水</v>
+        <v>火</v>
       </c>
       <c r="D166" s="13" t="str">
         <f>IF([1]攻守數據!AO167 = "", "", [1]攻守數據!AO167)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E166" s="13">
         <f>IF([1]攻守數據!AP167 = "", "", [1]攻守數據!AP167)</f>
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="F166" s="13" t="str">
         <f>IF([1]攻守數據!AQ167 = "", "", [1]攻守數據!AQ167)</f>
@@ -8783,19 +8792,19 @@
     <row r="167" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B167" s="13" t="str">
         <f>IF([1]攻守數據!AM168 = "", "", [1]攻守數據!AM168)</f>
-        <v>美納斯</v>
+        <v>鴨嘴炎獸</v>
       </c>
       <c r="C167" s="13" t="str">
         <f>IF([1]攻守數據!AN168 = "", "", [1]攻守數據!AN168)</f>
-        <v>龍</v>
+        <v>格鬥</v>
       </c>
       <c r="D167" s="13" t="str">
         <f>IF([1]攻守數據!AO168 = "", "", [1]攻守數據!AO168)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E167" s="13">
         <f>IF([1]攻守數據!AP168 = "", "", [1]攻守數據!AP168)</f>
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="F167" s="13" t="str">
         <f>IF([1]攻守數據!AQ168 = "", "", [1]攻守數據!AQ168)</f>
@@ -8805,19 +8814,19 @@
     <row r="168" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B168" s="13" t="str">
         <f>IF([1]攻守數據!AM169 = "", "", [1]攻守數據!AM169)</f>
-        <v>鴨嘴炎獸</v>
+        <v>超甲狂犀</v>
       </c>
       <c r="C168" s="13" t="str">
         <f>IF([1]攻守數據!AN169 = "", "", [1]攻守數據!AN169)</f>
-        <v>火</v>
+        <v>地面</v>
       </c>
       <c r="D168" s="13" t="str">
         <f>IF([1]攻守數據!AO169 = "", "", [1]攻守數據!AO169)</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E168" s="13">
         <f>IF([1]攻守數據!AP169 = "", "", [1]攻守數據!AP169)</f>
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F168" s="13" t="str">
         <f>IF([1]攻守數據!AQ169 = "", "", [1]攻守數據!AQ169)</f>
@@ -8827,19 +8836,19 @@
     <row r="169" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B169" s="13" t="str">
         <f>IF([1]攻守數據!AM170 = "", "", [1]攻守數據!AM170)</f>
-        <v>鴨嘴炎獸</v>
+        <v>超甲狂犀</v>
       </c>
       <c r="C169" s="13" t="str">
         <f>IF([1]攻守數據!AN170 = "", "", [1]攻守數據!AN170)</f>
-        <v>格鬥</v>
+        <v>岩石</v>
       </c>
       <c r="D169" s="13" t="str">
         <f>IF([1]攻守數據!AO170 = "", "", [1]攻守數據!AO170)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E169" s="13">
         <f>IF([1]攻守數據!AP170 = "", "", [1]攻守數據!AP170)</f>
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F169" s="13" t="str">
         <f>IF([1]攻守數據!AQ170 = "", "", [1]攻守數據!AQ170)</f>
@@ -8849,11 +8858,11 @@
     <row r="170" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B170" s="13" t="str">
         <f>IF([1]攻守數據!AM171 = "", "", [1]攻守數據!AM171)</f>
-        <v>超甲狂犀</v>
+        <v>帝牙盧卡</v>
       </c>
       <c r="C170" s="13" t="str">
         <f>IF([1]攻守數據!AN171 = "", "", [1]攻守數據!AN171)</f>
-        <v>地面</v>
+        <v>鋼</v>
       </c>
       <c r="D170" s="13" t="str">
         <f>IF([1]攻守數據!AO171 = "", "", [1]攻守數據!AO171)</f>
@@ -8861,7 +8870,7 @@
       </c>
       <c r="E170" s="13">
         <f>IF([1]攻守數據!AP171 = "", "", [1]攻守數據!AP171)</f>
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="F170" s="13" t="str">
         <f>IF([1]攻守數據!AQ171 = "", "", [1]攻守數據!AQ171)</f>
@@ -8871,11 +8880,11 @@
     <row r="171" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B171" s="13" t="str">
         <f>IF([1]攻守數據!AM172 = "", "", [1]攻守數據!AM172)</f>
-        <v>超甲狂犀</v>
+        <v>帝牙盧卡</v>
       </c>
       <c r="C171" s="13" t="str">
         <f>IF([1]攻守數據!AN172 = "", "", [1]攻守數據!AN172)</f>
-        <v>岩石</v>
+        <v>龍</v>
       </c>
       <c r="D171" s="13" t="str">
         <f>IF([1]攻守數據!AO172 = "", "", [1]攻守數據!AO172)</f>
@@ -8883,7 +8892,7 @@
       </c>
       <c r="E171" s="13">
         <f>IF([1]攻守數據!AP172 = "", "", [1]攻守數據!AP172)</f>
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="F171" s="13" t="str">
         <f>IF([1]攻守數據!AQ172 = "", "", [1]攻守數據!AQ172)</f>
@@ -8893,11 +8902,11 @@
     <row r="172" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B172" s="13" t="str">
         <f>IF([1]攻守數據!AM173 = "", "", [1]攻守數據!AM173)</f>
-        <v>帝牙盧卡</v>
+        <v>帕路奇亞</v>
       </c>
       <c r="C172" s="13" t="str">
         <f>IF([1]攻守數據!AN173 = "", "", [1]攻守數據!AN173)</f>
-        <v>鋼</v>
+        <v>龍</v>
       </c>
       <c r="D172" s="13" t="str">
         <f>IF([1]攻守數據!AO173 = "", "", [1]攻守數據!AO173)</f>
@@ -8905,7 +8914,7 @@
       </c>
       <c r="E172" s="13">
         <f>IF([1]攻守數據!AP173 = "", "", [1]攻守數據!AP173)</f>
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="F172" s="13" t="str">
         <f>IF([1]攻守數據!AQ173 = "", "", [1]攻守數據!AQ173)</f>
@@ -8915,11 +8924,11 @@
     <row r="173" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B173" s="13" t="str">
         <f>IF([1]攻守數據!AM174 = "", "", [1]攻守數據!AM174)</f>
-        <v>帝牙盧卡</v>
+        <v>瑪狃拉</v>
       </c>
       <c r="C173" s="13" t="str">
         <f>IF([1]攻守數據!AN174 = "", "", [1]攻守數據!AN174)</f>
-        <v>龍</v>
+        <v>冰</v>
       </c>
       <c r="D173" s="13" t="str">
         <f>IF([1]攻守數據!AO174 = "", "", [1]攻守數據!AO174)</f>
@@ -8927,7 +8936,7 @@
       </c>
       <c r="E173" s="13">
         <f>IF([1]攻守數據!AP174 = "", "", [1]攻守數據!AP174)</f>
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="F173" s="13" t="str">
         <f>IF([1]攻守數據!AQ174 = "", "", [1]攻守數據!AQ174)</f>
@@ -8937,11 +8946,11 @@
     <row r="174" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B174" s="13" t="str">
         <f>IF([1]攻守數據!AM175 = "", "", [1]攻守數據!AM175)</f>
-        <v>帕路奇亞</v>
+        <v>超極巨鋁鋼龍</v>
       </c>
       <c r="C174" s="13" t="str">
         <f>IF([1]攻守數據!AN175 = "", "", [1]攻守數據!AN175)</f>
-        <v>龍</v>
+        <v>鋼</v>
       </c>
       <c r="D174" s="13" t="str">
         <f>IF([1]攻守數據!AO175 = "", "", [1]攻守數據!AO175)</f>
@@ -8949,21 +8958,21 @@
       </c>
       <c r="E174" s="13">
         <f>IF([1]攻守數據!AP175 = "", "", [1]攻守數據!AP175)</f>
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="F174" s="13" t="str">
         <f>IF([1]攻守數據!AQ175 = "", "", [1]攻守數據!AQ175)</f>
-        <v>D</v>
+        <v>G</v>
       </c>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B175" s="13" t="str">
         <f>IF([1]攻守數據!AM176 = "", "", [1]攻守數據!AM176)</f>
-        <v>超極巨鋁鋼龍</v>
+        <v>瑪狃拉</v>
       </c>
       <c r="C175" s="13" t="str">
         <f>IF([1]攻守數據!AN176 = "", "", [1]攻守數據!AN176)</f>
-        <v>鋼</v>
+        <v>惡</v>
       </c>
       <c r="D175" s="13" t="str">
         <f>IF([1]攻守數據!AO176 = "", "", [1]攻守數據!AO176)</f>
@@ -8971,55 +8980,55 @@
       </c>
       <c r="E175" s="13">
         <f>IF([1]攻守數據!AP176 = "", "", [1]攻守數據!AP176)</f>
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F175" s="13" t="str">
         <f>IF([1]攻守數據!AQ176 = "", "", [1]攻守數據!AQ176)</f>
-        <v>G</v>
+        <v>D</v>
       </c>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B176" s="13" t="str">
         <f>IF([1]攻守數據!AM177 = "", "", [1]攻守數據!AM177)</f>
-        <v/>
+        <v>焚焰蚣</v>
       </c>
       <c r="C176" s="13" t="str">
         <f>IF([1]攻守數據!AN177 = "", "", [1]攻守數據!AN177)</f>
-        <v/>
+        <v>火</v>
       </c>
       <c r="D176" s="13" t="str">
         <f>IF([1]攻守數據!AO177 = "", "", [1]攻守數據!AO177)</f>
-        <v/>
-      </c>
-      <c r="E176" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E176" s="13">
         <f>IF([1]攻守數據!AP177 = "", "", [1]攻守數據!AP177)</f>
-        <v/>
+        <v>186</v>
       </c>
       <c r="F176" s="13" t="str">
         <f>IF([1]攻守數據!AQ177 = "", "", [1]攻守數據!AQ177)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B177" s="13" t="str">
         <f>IF([1]攻守數據!AM178 = "", "", [1]攻守數據!AM178)</f>
-        <v/>
+        <v>焚焰蚣</v>
       </c>
       <c r="C177" s="13" t="str">
         <f>IF([1]攻守數據!AN178 = "", "", [1]攻守數據!AN178)</f>
-        <v/>
+        <v>蟲</v>
       </c>
       <c r="D177" s="13" t="str">
         <f>IF([1]攻守數據!AO178 = "", "", [1]攻守數據!AO178)</f>
-        <v/>
-      </c>
-      <c r="E177" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E177" s="13">
         <f>IF([1]攻守數據!AP178 = "", "", [1]攻守數據!AP178)</f>
-        <v/>
+        <v>186</v>
       </c>
       <c r="F177" s="13" t="str">
         <f>IF([1]攻守數據!AQ178 = "", "", [1]攻守數據!AQ178)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.3">
@@ -9033,7 +9042,7 @@
       </c>
       <c r="D178" s="13" t="str">
         <f>IF([1]攻守數據!AO179 = "", "", [1]攻守數據!AO179)</f>
-        <v/>
+        <v>Y</v>
       </c>
       <c r="E178" s="13" t="str">
         <f>IF([1]攻守數據!AP179 = "", "", [1]攻守數據!AP179)</f>

--- a/Att.xlsx
+++ b/Att.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\寶可夢\Pokemon_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35066DD0-B7A1-43F9-AA4C-2B362B723445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932A32A9-F22D-4DDD-BE9A-B46B5122A4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3168,7 +3168,7 @@
             <v>地面</v>
           </cell>
           <cell r="AO169" t="str">
-            <v>N</v>
+            <v>Y</v>
           </cell>
           <cell r="AP169">
             <v>202</v>
@@ -3332,47 +3332,53 @@
         </row>
         <row r="179">
           <cell r="AM179" t="str">
-            <v/>
+            <v>由克希</v>
           </cell>
           <cell r="AN179" t="str">
-            <v/>
+            <v>超能力</v>
           </cell>
           <cell r="AO179" t="str">
             <v>Y</v>
           </cell>
-          <cell r="AP179" t="str">
-            <v/>
+          <cell r="AP179">
+            <v>135</v>
           </cell>
           <cell r="AQ179" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="180">
           <cell r="AM180" t="str">
-            <v/>
+            <v>艾姆利多</v>
           </cell>
           <cell r="AN180" t="str">
-            <v/>
-          </cell>
-          <cell r="AP180" t="str">
-            <v/>
+            <v>超能力</v>
+          </cell>
+          <cell r="AO180" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP180">
+            <v>179</v>
           </cell>
           <cell r="AQ180" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="181">
           <cell r="AM181" t="str">
-            <v/>
+            <v>亞克諾姆</v>
           </cell>
           <cell r="AN181" t="str">
-            <v/>
-          </cell>
-          <cell r="AP181" t="str">
-            <v/>
+            <v>超能力</v>
+          </cell>
+          <cell r="AO181" t="str">
+            <v>Y</v>
+          </cell>
+          <cell r="AP181">
+            <v>225</v>
           </cell>
           <cell r="AQ181" t="str">
-            <v/>
+            <v>D</v>
           </cell>
         </row>
         <row r="182">
@@ -8822,7 +8828,7 @@
       </c>
       <c r="D168" s="13" t="str">
         <f>IF([1]攻守數據!AO169 = "", "", [1]攻守數據!AO169)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E168" s="13">
         <f>IF([1]攻守數據!AP169 = "", "", [1]攻守數據!AP169)</f>
@@ -9034,67 +9040,67 @@
     <row r="178" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B178" s="13" t="str">
         <f>IF([1]攻守數據!AM179 = "", "", [1]攻守數據!AM179)</f>
-        <v/>
+        <v>由克希</v>
       </c>
       <c r="C178" s="13" t="str">
         <f>IF([1]攻守數據!AN179 = "", "", [1]攻守數據!AN179)</f>
-        <v/>
+        <v>超能力</v>
       </c>
       <c r="D178" s="13" t="str">
         <f>IF([1]攻守數據!AO179 = "", "", [1]攻守數據!AO179)</f>
         <v>Y</v>
       </c>
-      <c r="E178" s="13" t="str">
+      <c r="E178" s="13">
         <f>IF([1]攻守數據!AP179 = "", "", [1]攻守數據!AP179)</f>
-        <v/>
+        <v>135</v>
       </c>
       <c r="F178" s="13" t="str">
         <f>IF([1]攻守數據!AQ179 = "", "", [1]攻守數據!AQ179)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="179" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B179" s="13" t="str">
         <f>IF([1]攻守數據!AM180 = "", "", [1]攻守數據!AM180)</f>
-        <v/>
+        <v>艾姆利多</v>
       </c>
       <c r="C179" s="13" t="str">
         <f>IF([1]攻守數據!AN180 = "", "", [1]攻守數據!AN180)</f>
-        <v/>
+        <v>超能力</v>
       </c>
       <c r="D179" s="13" t="str">
         <f>IF([1]攻守數據!AO180 = "", "", [1]攻守數據!AO180)</f>
-        <v/>
-      </c>
-      <c r="E179" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E179" s="13">
         <f>IF([1]攻守數據!AP180 = "", "", [1]攻守數據!AP180)</f>
-        <v/>
+        <v>179</v>
       </c>
       <c r="F179" s="13" t="str">
         <f>IF([1]攻守數據!AQ180 = "", "", [1]攻守數據!AQ180)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="180" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B180" s="13" t="str">
         <f>IF([1]攻守數據!AM181 = "", "", [1]攻守數據!AM181)</f>
-        <v/>
+        <v>亞克諾姆</v>
       </c>
       <c r="C180" s="13" t="str">
         <f>IF([1]攻守數據!AN181 = "", "", [1]攻守數據!AN181)</f>
-        <v/>
+        <v>超能力</v>
       </c>
       <c r="D180" s="13" t="str">
         <f>IF([1]攻守數據!AO181 = "", "", [1]攻守數據!AO181)</f>
-        <v/>
-      </c>
-      <c r="E180" s="13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E180" s="13">
         <f>IF([1]攻守數據!AP181 = "", "", [1]攻守數據!AP181)</f>
-        <v/>
+        <v>225</v>
       </c>
       <c r="F180" s="13" t="str">
         <f>IF([1]攻守數據!AQ181 = "", "", [1]攻守數據!AQ181)</f>
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="181" spans="2:6" x14ac:dyDescent="0.3">

--- a/Att.xlsx
+++ b/Att.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\寶可夢\Pokemon_App\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\100.127.78.90\Elton\備分\寶可夢\Pokemon_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932A32A9-F22D-4DDD-BE9A-B46B5122A4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -322,6 +322,9 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
+          <cell r="AG2" t="str">
+            <v>寶可夢</v>
+          </cell>
           <cell r="AM2" t="str">
             <v>寶可夢</v>
           </cell>
@@ -3936,7 +3939,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AB200"/>
-  <sheetFormatPr defaultRowHeight="15.65" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
@@ -4025,7 +4028,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B2" s="13" t="str">
         <f>IF([1]攻守數據!AM3 = "", "", [1]攻守數據!AM3)</f>
         <v>超極巨轟擂金剛猩</v>
@@ -4189,7 +4192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="str">
         <f>IF([1]攻守數據!AM5 = "", "", [1]攻守數據!AM5)</f>
         <v>超極巨怪力</v>
@@ -4517,7 +4520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="str">
         <f>IF([1]攻守數據!AM9 = "", "", [1]攻守數據!AM9)</f>
         <v>超極巨顫弦蠑螈</v>
@@ -4599,7 +4602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="str">
         <f>IF([1]攻守數據!AM10 = "", "", [1]攻守數據!AM10)</f>
         <v>顫弦蠑螈</v>
@@ -4681,7 +4684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="str">
         <f>IF([1]攻守數據!AM11 = "", "", [1]攻守數據!AM11)</f>
         <v>顫弦蠑螈</v>
@@ -4763,7 +4766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="str">
         <f>IF([1]攻守數據!AM12 = "", "", [1]攻守數據!AM12)</f>
         <v>超極巨妙蛙花</v>
@@ -5091,7 +5094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="str">
         <f>IF([1]攻守數據!AM16 = "", "", [1]攻守數據!AM16)</f>
         <v>閃電鳥</v>
@@ -5173,7 +5176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:28" ht="16.3" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:28" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="str">
         <f>IF([1]攻守數據!AM17 = "", "", [1]攻守數據!AM17)</f>
         <v>雷公</v>
